--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7CD66C-84B8-47AA-8ECC-EA22FA1C659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E8904BD-8396-407A-BCFF-2A10FB41648F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>today I met my mother</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>I was feeling very sad</t>
   </si>
 </sst>
 </file>
@@ -1771,27 +1777,51 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+    <row r="22" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B22" s="14">
+        <v>480</v>
+      </c>
+      <c r="C22" s="14">
+        <v>90</v>
+      </c>
+      <c r="D22" s="14">
+        <v>50</v>
+      </c>
+      <c r="E22" s="14">
+        <v>80</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>80</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E8904BD-8396-407A-BCFF-2A10FB41648F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308D5D80-9B8C-4AAD-82BD-26CFE74A245F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1824,26 +1824,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B23" s="14">
+        <v>360</v>
+      </c>
+      <c r="C23" s="14">
+        <v>80</v>
+      </c>
+      <c r="D23" s="14">
+        <v>60</v>
+      </c>
+      <c r="E23" s="14">
+        <v>80</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>80</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308D5D80-9B8C-4AAD-82BD-26CFE74A245F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964D43A3-BED1-4E6F-97A9-AD888D954B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>I was feeling very sad</t>
+  </si>
+  <si>
+    <t>a calm and relaxed day</t>
   </si>
 </sst>
 </file>
@@ -1870,26 +1873,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B24" s="14">
+        <v>180</v>
+      </c>
+      <c r="C24" s="14">
+        <v>90</v>
+      </c>
+      <c r="D24" s="14">
+        <v>120</v>
+      </c>
+      <c r="E24" s="14">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14">
+        <v>300</v>
+      </c>
+      <c r="G24" s="14">
+        <v>6</v>
+      </c>
+      <c r="H24" s="14">
+        <v>90</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{964D43A3-BED1-4E6F-97A9-AD888D954B7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4C3344-3517-4182-9F1C-F8CA711C54E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1919,26 +1919,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B25" s="14">
+        <v>480</v>
+      </c>
+      <c r="C25" s="14">
+        <v>90</v>
+      </c>
+      <c r="D25" s="14">
+        <v>60</v>
+      </c>
+      <c r="E25" s="14">
+        <v>40</v>
+      </c>
+      <c r="F25" s="14">
+        <v>250</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="14">
+        <v>120</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4C3344-3517-4182-9F1C-F8CA711C54E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01423AF2-D8F6-4F42-97A2-5AC35DD5F4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1965,26 +1965,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B26" s="14">
+        <v>300</v>
+      </c>
+      <c r="C26" s="14">
+        <v>100</v>
+      </c>
+      <c r="D26" s="14">
+        <v>80</v>
+      </c>
+      <c r="E26" s="14">
+        <v>70</v>
+      </c>
+      <c r="F26" s="14">
+        <v>250</v>
+      </c>
+      <c r="G26" s="14">
+        <v>5</v>
+      </c>
+      <c r="H26" s="14">
+        <v>130</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>930</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>510</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01423AF2-D8F6-4F42-97A2-5AC35DD5F4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE7E40B-5B3A-41A6-BBD0-1C350EF211CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>a calm and relaxed day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interseting day &amp; fresher's patry </t>
   </si>
 </sst>
 </file>
@@ -2010,27 +2013,51 @@
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+    <row r="27" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B27" s="14">
+        <v>360</v>
+      </c>
+      <c r="C27" s="14">
+        <v>100</v>
+      </c>
+      <c r="D27" s="14">
+        <v>70</v>
+      </c>
+      <c r="E27" s="14">
+        <v>60</v>
+      </c>
+      <c r="F27" s="14">
+        <v>100</v>
+      </c>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDE7E40B-5B3A-41A6-BBD0-1C350EF211CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637FAEC8-8FB4-4DBE-99A5-C1F63BE03179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t xml:space="preserve">Interseting day &amp; fresher's patry </t>
+  </si>
+  <si>
+    <t>feeling tired</t>
   </si>
 </sst>
 </file>
@@ -2060,26 +2063,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B28" s="14">
+        <v>300</v>
+      </c>
+      <c r="C28" s="14">
+        <v>100</v>
+      </c>
+      <c r="D28" s="14">
+        <v>50</v>
+      </c>
+      <c r="E28" s="14">
+        <v>60</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>120</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637FAEC8-8FB4-4DBE-99A5-C1F63BE03179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B155521-40A1-4B98-8B9C-AF0593F15F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>feeling tired</t>
+  </si>
+  <si>
+    <t>A movie day with friends</t>
+  </si>
+  <si>
+    <t>sleepy all day</t>
   </si>
 </sst>
 </file>
@@ -2109,48 +2115,96 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B29" s="14">
+        <v>360</v>
+      </c>
+      <c r="C29" s="14">
+        <v>100</v>
+      </c>
+      <c r="D29" s="14">
+        <v>50</v>
+      </c>
+      <c r="E29" s="14">
+        <v>50</v>
+      </c>
+      <c r="F29" s="14">
+        <v>0</v>
+      </c>
+      <c r="G29" s="14">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14">
+        <v>300</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B30" s="14">
+        <v>300</v>
+      </c>
+      <c r="C30" s="14">
+        <v>30</v>
+      </c>
+      <c r="D30" s="14">
+        <v>40</v>
+      </c>
+      <c r="E30" s="14">
+        <v>40</v>
+      </c>
+      <c r="F30" s="14">
+        <v>0</v>
+      </c>
+      <c r="G30" s="14">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14">
+        <v>120</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>910</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+  <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B155521-40A1-4B98-8B9C-AF0593F15F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2897F4DD-253D-4A64-A5C9-43271AFD300C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2207,26 +2207,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B31" s="14">
+        <v>240</v>
+      </c>
+      <c r="C31" s="14">
+        <v>120</v>
+      </c>
+      <c r="D31" s="14">
+        <v>70</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>200</v>
+      </c>
+      <c r="G31" s="14">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>810</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>630</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2897F4DD-253D-4A64-A5C9-43271AFD300C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DF2678-FBC4-4F60-829F-CBD881EF656D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2253,26 +2253,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B32" s="14">
+        <v>240</v>
+      </c>
+      <c r="C32" s="14">
+        <v>120</v>
+      </c>
+      <c r="D32" s="14">
+        <v>60</v>
+      </c>
+      <c r="E32" s="14">
+        <v>80</v>
+      </c>
+      <c r="F32" s="14">
+        <v>250</v>
+      </c>
+      <c r="G32" s="14">
+        <v>5</v>
+      </c>
+      <c r="H32" s="14">
+        <v>150</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DF2678-FBC4-4F60-829F-CBD881EF656D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE1AC87-1521-4DD0-AA65-A8D7425563BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2299,26 +2299,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B33" s="14">
+        <v>300</v>
+      </c>
+      <c r="C33" s="14">
+        <v>120</v>
+      </c>
+      <c r="D33" s="14">
+        <v>80</v>
+      </c>
+      <c r="E33" s="14">
+        <v>70</v>
+      </c>
+      <c r="F33" s="14">
+        <v>150</v>
+      </c>
+      <c r="G33" s="14">
+        <v>3</v>
+      </c>
+      <c r="H33" s="14">
+        <v>150</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE1AC87-1521-4DD0-AA65-A8D7425563BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED63E4BE-6B52-4750-993D-D13DE103C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2345,26 +2345,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B34" s="14">
+        <v>240</v>
+      </c>
+      <c r="C34" s="14">
+        <v>120</v>
+      </c>
+      <c r="D34" s="14">
+        <v>70</v>
+      </c>
+      <c r="E34" s="14">
+        <v>80</v>
+      </c>
+      <c r="F34" s="14">
+        <v>300</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>160</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED63E4BE-6B52-4750-993D-D13DE103C8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767FC28E-29B4-47F9-B57A-E714DA67D28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>sleepy all day</t>
+  </si>
+  <si>
+    <t>high</t>
+  </si>
+  <si>
+    <t>CA 1 &amp; home day</t>
   </si>
 </sst>
 </file>
@@ -2391,48 +2397,96 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B35" s="14">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14">
+        <v>100</v>
+      </c>
+      <c r="D35" s="14">
+        <v>90</v>
+      </c>
+      <c r="E35" s="14">
+        <v>60</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>160</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B36" s="14">
+        <v>360</v>
+      </c>
+      <c r="C36" s="14">
+        <v>120</v>
+      </c>
+      <c r="D36" s="14">
+        <v>70</v>
+      </c>
+      <c r="E36" s="14">
+        <v>40</v>
+      </c>
+      <c r="F36" s="14">
+        <v>0</v>
+      </c>
+      <c r="G36" s="14">
+        <v>0</v>
+      </c>
+      <c r="H36" s="14">
+        <v>130</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767FC28E-29B4-47F9-B57A-E714DA67D28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001FC45F-0924-4565-8475-50E44D2FFDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,12 @@
   </si>
   <si>
     <t>CA 1 &amp; home day</t>
+  </si>
+  <si>
+    <t>2026-09-220</t>
+  </si>
+  <si>
+    <t>exhausted from traveling</t>
   </si>
 </sst>
 </file>
@@ -2489,26 +2495,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="A37" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>150</v>
+      </c>
+      <c r="D37" s="14">
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>180</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001FC45F-0924-4565-8475-50E44D2FFDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAC7D7D-77FE-4BEE-8E61-ADD87D735EAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,12 @@
   </si>
   <si>
     <t>exhausted from traveling</t>
+  </si>
+  <si>
+    <t>satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">relaxed day </t>
   </si>
 </sst>
 </file>
@@ -2541,26 +2547,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B38" s="14">
+        <v>300</v>
+      </c>
+      <c r="C38" s="14">
+        <v>120</v>
+      </c>
+      <c r="D38" s="14">
+        <v>50</v>
+      </c>
+      <c r="E38" s="14">
+        <v>70</v>
+      </c>
+      <c r="F38" s="14">
+        <v>200</v>
+      </c>
+      <c r="G38" s="14">
+        <v>4</v>
+      </c>
+      <c r="H38" s="14">
+        <v>140</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06439AE5-42F9-4E9B-82B4-3BC1E070E6BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130404EB-D143-41EE-B00E-58D8CF597E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1097,9 +1097,11 @@
         <v>60</v>
       </c>
       <c r="I6" s="15">
+        <f>IF(SUM(B6:F6,H6)=0," ",SUM(B6:F6,H6))</f>
         <v>800</v>
       </c>
       <c r="J6" s="15">
+        <f>IF(I6=" ","",1440-I6)</f>
         <v>640</v>
       </c>
       <c r="K6" s="16" t="s">
@@ -1140,13 +1142,13 @@
       <c r="H7" s="9">
         <v>80</v>
       </c>
-      <c r="I7" s="10">
-        <f t="shared" ref="I7:I69" si="0">IF(SUM(B6:F6,H7)=0,"",SUM(B6:F6,H7))</f>
-        <v>820</v>
-      </c>
-      <c r="J7" s="10">
-        <f t="shared" ref="J7:J69" si="1">IF(I7="","",1440-I7)</f>
-        <v>620</v>
+      <c r="I7" s="15">
+        <f t="shared" ref="I7:I41" si="0">IF(SUM(B7:F7,H7)=0," ",SUM(B7:F7,H7))</f>
+        <v>830</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" ref="J7:J70" si="1">IF(I7=" ","",1440-I7)</f>
+        <v>610</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>56</v>
@@ -1186,13 +1188,13 @@
       <c r="H8" s="9">
         <v>50</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
-      <c r="J8" s="10">
+        <v>520</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>920</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>59</v>
@@ -1232,13 +1234,13 @@
       <c r="H9" s="9">
         <v>60</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>530</v>
-      </c>
-      <c r="J9" s="10">
+        <v>490</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>910</v>
+        <v>950</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>59</v>
@@ -1278,13 +1280,13 @@
       <c r="H10" s="9">
         <v>30</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>460</v>
-      </c>
-      <c r="J10" s="10">
+        <v>610</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>980</v>
+        <v>830</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>59</v>
@@ -1324,13 +1326,13 @@
       <c r="H11" s="9">
         <v>60</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>640</v>
-      </c>
-      <c r="J11" s="10">
+        <v>715</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>800</v>
+        <v>725</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>49</v>
@@ -1370,13 +1372,13 @@
       <c r="H12" s="9">
         <v>70</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>725</v>
-      </c>
-      <c r="J12" s="10">
+        <v>740</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>59</v>
@@ -1416,13 +1418,13 @@
       <c r="H13" s="9">
         <v>40</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>710</v>
-      </c>
-      <c r="J13" s="10">
+        <v>810</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>730</v>
+        <v>630</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>49</v>
@@ -1462,13 +1464,13 @@
       <c r="H14" s="9">
         <v>70</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
-      </c>
-      <c r="J14" s="10">
+        <v>780</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>57</v>
@@ -1508,13 +1510,13 @@
       <c r="H15" s="9">
         <v>70</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J15" s="15">
+        <f t="shared" si="1"/>
         <v>780</v>
-      </c>
-      <c r="J15" s="10">
-        <f t="shared" si="1"/>
-        <v>660</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>59</v>
@@ -1554,13 +1556,13 @@
       <c r="H16" s="9">
         <v>80</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>670</v>
-      </c>
-      <c r="J16" s="10">
+        <v>500</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>770</v>
+        <v>940</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>58</v>
@@ -1600,13 +1602,13 @@
       <c r="H17" s="9">
         <v>90</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>510</v>
-      </c>
-      <c r="J17" s="10">
+        <v>690</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>930</v>
+        <v>750</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>49</v>
@@ -1646,13 +1648,13 @@
       <c r="H18" s="9">
         <v>80</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>680</v>
-      </c>
-      <c r="J18" s="10">
+        <v>980</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>760</v>
+        <v>460</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>57</v>
@@ -1692,13 +1694,13 @@
       <c r="H19" s="9">
         <v>70</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>970</v>
-      </c>
-      <c r="J19" s="10">
+        <v>770</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>470</v>
+        <v>670</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>58</v>
@@ -1738,13 +1740,13 @@
       <c r="H20" s="9">
         <v>80</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>780</v>
-      </c>
-      <c r="J20" s="10">
+        <v>820</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>620</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>57</v>
@@ -1784,13 +1786,13 @@
       <c r="H21" s="9">
         <v>90</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>830</v>
-      </c>
-      <c r="J21" s="10">
+        <v>1060</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>380</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>59</v>
@@ -1830,13 +1832,13 @@
       <c r="H22" s="9">
         <v>80</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
-      </c>
-      <c r="J22" s="10">
+        <v>660</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>780</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>58</v>
@@ -1876,13 +1878,13 @@
       <c r="H23" s="9">
         <v>80</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>660</v>
-      </c>
-      <c r="J23" s="10">
+        <v>480</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>960</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>49</v>
@@ -1922,13 +1924,13 @@
       <c r="H24" s="9">
         <v>90</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>490</v>
-      </c>
-      <c r="J24" s="10">
+        <v>1200</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>950</v>
+        <v>240</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>49</v>
@@ -1968,13 +1970,13 @@
       <c r="H25" s="9">
         <v>120</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>1230</v>
-      </c>
-      <c r="J25" s="10">
+        <v>860</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>210</v>
+        <v>580</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>59</v>
@@ -2014,13 +2016,13 @@
       <c r="H26" s="9">
         <v>130</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
-      </c>
-      <c r="J26" s="10">
+        <v>990</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>450</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>49</v>
@@ -2060,13 +2062,13 @@
       <c r="H27" s="9">
         <v>120</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>980</v>
-      </c>
-      <c r="J27" s="10">
+        <v>750</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>460</v>
+        <v>690</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>59</v>
@@ -2106,13 +2108,13 @@
       <c r="H28" s="9">
         <v>120</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>750</v>
-      </c>
-      <c r="J28" s="10">
+        <v>1040</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>690</v>
+        <v>400</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>57</v>
@@ -2152,13 +2154,13 @@
       <c r="H29" s="9">
         <v>300</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>1220</v>
-      </c>
-      <c r="J29" s="10">
+        <v>800</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>220</v>
+        <v>640</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>59</v>
@@ -2198,13 +2200,13 @@
       <c r="H30" s="9">
         <v>120</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>620</v>
-      </c>
-      <c r="J30" s="10">
+        <v>470</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>970</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>58</v>
@@ -2244,13 +2246,13 @@
       <c r="H31" s="9">
         <v>120</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>470</v>
-      </c>
-      <c r="J31" s="10">
+        <v>810</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>970</v>
+        <v>630</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>49</v>
@@ -2290,13 +2292,13 @@
       <c r="H32" s="9">
         <v>150</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
-      </c>
-      <c r="J32" s="10">
+        <v>960</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>59</v>
@@ -2336,13 +2338,13 @@
       <c r="H33" s="9">
         <v>150</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
-      </c>
-      <c r="J33" s="10">
+        <v>810</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>57</v>
@@ -2382,13 +2384,13 @@
       <c r="H34" s="9">
         <v>160</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>820</v>
-      </c>
-      <c r="J34" s="10">
+        <v>1030</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>620</v>
+        <v>410</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>59</v>
@@ -2428,13 +2430,13 @@
       <c r="H35" s="9">
         <v>160</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1030</v>
-      </c>
-      <c r="J35" s="10">
+        <v>1120</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>59</v>
@@ -2474,13 +2476,13 @@
       <c r="H36" s="9">
         <v>130</v>
       </c>
-      <c r="I36" s="10">
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>1090</v>
-      </c>
-      <c r="J36" s="10">
+        <v>780</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>660</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>59</v>
@@ -2520,13 +2522,13 @@
       <c r="H37" s="9">
         <v>180</v>
       </c>
-      <c r="I37" s="10">
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>830</v>
-      </c>
-      <c r="J37" s="10">
+        <v>630</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>810</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>58</v>
@@ -2566,13 +2568,13 @@
       <c r="H38" s="9">
         <v>140</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>590</v>
-      </c>
-      <c r="J38" s="10">
+        <v>880</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>850</v>
+        <v>560</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>49</v>
@@ -2612,13 +2614,13 @@
       <c r="H39" s="9">
         <v>120</v>
       </c>
-      <c r="I39" s="10">
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>860</v>
-      </c>
-      <c r="J39" s="10">
+        <v>970</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>470</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>59</v>
@@ -2634,23 +2636,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10" t="str">
+      <c r="A40" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B40" s="9">
+        <v>270</v>
+      </c>
+      <c r="C40" s="9">
+        <v>130</v>
+      </c>
+      <c r="D40" s="9">
+        <v>80</v>
+      </c>
+      <c r="E40" s="9">
+        <v>70</v>
+      </c>
+      <c r="F40" s="9">
+        <v>200</v>
+      </c>
+      <c r="G40" s="9">
+        <v>4</v>
+      </c>
+      <c r="H40" s="9">
+        <v>150</v>
+      </c>
+      <c r="I40" s="15">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="12"/>
+        <v>540</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="12" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="8"/>
@@ -2661,11 +2690,11 @@
       <c r="F41" s="9"/>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
-      <c r="I41" s="10" t="str">
+      <c r="I41" s="15" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="10" t="str">
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J41" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2683,11 +2712,11 @@
       <c r="F42" s="9"/>
       <c r="G42" s="9"/>
       <c r="H42" s="9"/>
-      <c r="I42" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="10" t="str">
+      <c r="I42" s="15" t="str">
+        <f t="shared" ref="I42:I70" si="2">IF(SUM(B42:F42,H42)=0," ",SUM(B42:F42,H42))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J42" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2705,11 +2734,11 @@
       <c r="F43" s="9"/>
       <c r="G43" s="9"/>
       <c r="H43" s="9"/>
-      <c r="I43" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="10" t="str">
+      <c r="I43" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J43" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2727,11 +2756,11 @@
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
-      <c r="I44" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="10" t="str">
+      <c r="I44" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J44" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2749,11 +2778,11 @@
       <c r="F45" s="9"/>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
-      <c r="I45" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="10" t="str">
+      <c r="I45" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J45" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2771,11 +2800,11 @@
       <c r="F46" s="9"/>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
-      <c r="I46" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="10" t="str">
+      <c r="I46" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J46" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2793,11 +2822,11 @@
       <c r="F47" s="9"/>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
-      <c r="I47" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="10" t="str">
+      <c r="I47" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J47" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2815,11 +2844,11 @@
       <c r="F48" s="9"/>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
-      <c r="I48" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="10" t="str">
+      <c r="I48" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J48" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2837,11 +2866,11 @@
       <c r="F49" s="9"/>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
-      <c r="I49" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="10" t="str">
+      <c r="I49" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J49" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2859,11 +2888,11 @@
       <c r="F50" s="9"/>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
-      <c r="I50" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="10" t="str">
+      <c r="I50" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J50" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2881,11 +2910,11 @@
       <c r="F51" s="9"/>
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
-      <c r="I51" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="10" t="str">
+      <c r="I51" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J51" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2903,11 +2932,11 @@
       <c r="F52" s="9"/>
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
-      <c r="I52" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="10" t="str">
+      <c r="I52" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J52" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2925,11 +2954,11 @@
       <c r="F53" s="9"/>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
-      <c r="I53" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="10" t="str">
+      <c r="I53" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J53" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2947,11 +2976,11 @@
       <c r="F54" s="9"/>
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
-      <c r="I54" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="10" t="str">
+      <c r="I54" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J54" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2969,11 +2998,11 @@
       <c r="F55" s="9"/>
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
-      <c r="I55" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="10" t="str">
+      <c r="I55" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J55" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2991,11 +3020,11 @@
       <c r="F56" s="9"/>
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
-      <c r="I56" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="10" t="str">
+      <c r="I56" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J56" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3013,11 +3042,11 @@
       <c r="F57" s="9"/>
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
-      <c r="I57" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="10" t="str">
+      <c r="I57" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J57" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3035,11 +3064,11 @@
       <c r="F58" s="9"/>
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
-      <c r="I58" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="10" t="str">
+      <c r="I58" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J58" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3057,11 +3086,11 @@
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
-      <c r="I59" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="10" t="str">
+      <c r="I59" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J59" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3079,11 +3108,11 @@
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
-      <c r="I60" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="10" t="str">
+      <c r="I60" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J60" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3101,11 +3130,11 @@
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
-      <c r="I61" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="10" t="str">
+      <c r="I61" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J61" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3123,11 +3152,11 @@
       <c r="F62" s="9"/>
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
-      <c r="I62" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="10" t="str">
+      <c r="I62" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J62" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3145,11 +3174,11 @@
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
-      <c r="I63" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="10" t="str">
+      <c r="I63" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J63" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3167,11 +3196,11 @@
       <c r="F64" s="9"/>
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
-      <c r="I64" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="10" t="str">
+      <c r="I64" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J64" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3189,11 +3218,11 @@
       <c r="F65" s="9"/>
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
-      <c r="I65" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="10" t="str">
+      <c r="I65" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J65" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3211,11 +3240,11 @@
       <c r="F66" s="9"/>
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
-      <c r="I66" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="10" t="str">
+      <c r="I66" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J66" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3233,11 +3262,11 @@
       <c r="F67" s="9"/>
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
-      <c r="I67" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="10" t="str">
+      <c r="I67" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J67" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3255,11 +3284,11 @@
       <c r="F68" s="9"/>
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
-      <c r="I68" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="10" t="str">
+      <c r="I68" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J68" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3277,11 +3306,11 @@
       <c r="F69" s="9"/>
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
-      <c r="I69" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="10" t="str">
+      <c r="I69" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J69" s="15" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3299,12 +3328,12 @@
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
-      <c r="I70" s="10" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B69:F69,H70)=0,"",SUM(B69:F69,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="10" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+      <c r="I70" s="15" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J70" s="15" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3321,12 +3350,12 @@
       <c r="F71" s="9"/>
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
-      <c r="I71" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="10" t="str">
-        <f t="shared" si="3"/>
+      <c r="I71" s="15" t="str">
+        <f t="shared" ref="I71:I114" si="3">IF(SUM(B71:F71,H71)=0," ",SUM(B71:F71,H71))</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J71" s="15" t="str">
+        <f t="shared" ref="J71:J114" si="4">IF(I71=" ","",1440-I71)</f>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3343,12 +3372,12 @@
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
-      <c r="I72" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="10" t="str">
+      <c r="I72" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J72" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3365,12 +3394,12 @@
       <c r="F73" s="9"/>
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
-      <c r="I73" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="10" t="str">
+      <c r="I73" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J73" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3387,12 +3416,12 @@
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
-      <c r="I74" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="10" t="str">
+      <c r="I74" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J74" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3409,12 +3438,12 @@
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
-      <c r="I75" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="10" t="str">
+      <c r="I75" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J75" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3431,12 +3460,12 @@
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
-      <c r="I76" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="10" t="str">
+      <c r="I76" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J76" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3453,12 +3482,12 @@
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
-      <c r="I77" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="10" t="str">
+      <c r="I77" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J77" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3475,12 +3504,12 @@
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
-      <c r="I78" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="10" t="str">
+      <c r="I78" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J78" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3497,12 +3526,12 @@
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
-      <c r="I79" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="10" t="str">
+      <c r="I79" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J79" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3519,12 +3548,12 @@
       <c r="F80" s="9"/>
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
-      <c r="I80" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="10" t="str">
+      <c r="I80" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J80" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3541,12 +3570,12 @@
       <c r="F81" s="9"/>
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
-      <c r="I81" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="10" t="str">
+      <c r="I81" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J81" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3563,12 +3592,12 @@
       <c r="F82" s="9"/>
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
-      <c r="I82" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J82" s="10" t="str">
+      <c r="I82" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J82" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3585,12 +3614,12 @@
       <c r="F83" s="9"/>
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
-      <c r="I83" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J83" s="10" t="str">
+      <c r="I83" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J83" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3607,12 +3636,12 @@
       <c r="F84" s="9"/>
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
-      <c r="I84" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J84" s="10" t="str">
+      <c r="I84" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J84" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3629,12 +3658,12 @@
       <c r="F85" s="9"/>
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
-      <c r="I85" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J85" s="10" t="str">
+      <c r="I85" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J85" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3651,12 +3680,12 @@
       <c r="F86" s="9"/>
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
-      <c r="I86" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J86" s="10" t="str">
+      <c r="I86" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J86" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3673,12 +3702,12 @@
       <c r="F87" s="9"/>
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
-      <c r="I87" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J87" s="10" t="str">
+      <c r="I87" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J87" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3695,12 +3724,12 @@
       <c r="F88" s="9"/>
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
-      <c r="I88" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J88" s="10" t="str">
+      <c r="I88" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J88" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3717,12 +3746,12 @@
       <c r="F89" s="9"/>
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
-      <c r="I89" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J89" s="10" t="str">
+      <c r="I89" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J89" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3739,12 +3768,12 @@
       <c r="F90" s="9"/>
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
-      <c r="I90" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J90" s="10" t="str">
+      <c r="I90" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J90" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3761,12 +3790,12 @@
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
-      <c r="I91" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J91" s="10" t="str">
+      <c r="I91" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J91" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3783,12 +3812,12 @@
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
-      <c r="I92" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J92" s="10" t="str">
+      <c r="I92" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J92" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3805,12 +3834,12 @@
       <c r="F93" s="9"/>
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
-      <c r="I93" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J93" s="10" t="str">
+      <c r="I93" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J93" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3827,12 +3856,12 @@
       <c r="F94" s="9"/>
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
-      <c r="I94" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J94" s="10" t="str">
+      <c r="I94" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J94" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3849,12 +3878,12 @@
       <c r="F95" s="9"/>
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
-      <c r="I95" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J95" s="10" t="str">
+      <c r="I95" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J95" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3871,12 +3900,12 @@
       <c r="F96" s="9"/>
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
-      <c r="I96" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J96" s="10" t="str">
+      <c r="I96" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J96" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3893,12 +3922,12 @@
       <c r="F97" s="9"/>
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
-      <c r="I97" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J97" s="10" t="str">
+      <c r="I97" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J97" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3915,12 +3944,12 @@
       <c r="F98" s="9"/>
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
-      <c r="I98" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J98" s="10" t="str">
+      <c r="I98" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J98" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -3937,12 +3966,12 @@
       <c r="F99" s="9"/>
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
-      <c r="I99" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J99" s="10" t="str">
+      <c r="I99" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J99" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -3959,12 +3988,12 @@
       <c r="F100" s="9"/>
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
-      <c r="I100" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J100" s="10" t="str">
+      <c r="I100" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J100" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -3981,12 +4010,12 @@
       <c r="F101" s="9"/>
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
-      <c r="I101" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J101" s="10" t="str">
+      <c r="I101" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J101" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4003,12 +4032,12 @@
       <c r="F102" s="9"/>
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
-      <c r="I102" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J102" s="10" t="str">
+      <c r="I102" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J102" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4025,12 +4054,12 @@
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
-      <c r="I103" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J103" s="10" t="str">
+      <c r="I103" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J103" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4047,12 +4076,12 @@
       <c r="F104" s="9"/>
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
-      <c r="I104" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J104" s="10" t="str">
+      <c r="I104" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J104" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4069,12 +4098,12 @@
       <c r="F105" s="9"/>
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
-      <c r="I105" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J105" s="10" t="str">
+      <c r="I105" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J105" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4091,12 +4120,12 @@
       <c r="F106" s="9"/>
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
-      <c r="I106" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J106" s="10" t="str">
+      <c r="I106" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J106" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4113,12 +4142,12 @@
       <c r="F107" s="9"/>
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
-      <c r="I107" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J107" s="10" t="str">
+      <c r="I107" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J107" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4135,12 +4164,12 @@
       <c r="F108" s="9"/>
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
-      <c r="I108" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J108" s="10" t="str">
+      <c r="I108" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J108" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4157,12 +4186,12 @@
       <c r="F109" s="9"/>
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
-      <c r="I109" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J109" s="10" t="str">
+      <c r="I109" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J109" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4179,12 +4208,12 @@
       <c r="F110" s="9"/>
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
-      <c r="I110" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J110" s="10" t="str">
+      <c r="I110" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J110" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4201,12 +4230,12 @@
       <c r="F111" s="9"/>
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
-      <c r="I111" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J111" s="10" t="str">
+      <c r="I111" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J111" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4223,12 +4252,12 @@
       <c r="F112" s="9"/>
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
-      <c r="I112" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J112" s="10" t="str">
+      <c r="I112" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J112" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4245,12 +4274,12 @@
       <c r="F113" s="9"/>
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
-      <c r="I113" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J113" s="10" t="str">
+      <c r="I113" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J113" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4267,12 +4296,12 @@
       <c r="F114" s="9"/>
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
-      <c r="I114" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J114" s="10" t="str">
+      <c r="I114" s="15" t="str">
         <f t="shared" si="3"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J114" s="15" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4290,13 +4319,10 @@
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
       <c r="I115" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J115" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+        <f t="shared" ref="I115:I133" si="5">IF(SUM(B114:F114,H115)=0,"",SUM(B114:F114,H115))</f>
+        <v/>
+      </c>
+      <c r="J115" s="15"/>
       <c r="K115" s="11"/>
       <c r="L115" s="11"/>
       <c r="M115" s="11"/>
@@ -4312,13 +4338,10 @@
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
       <c r="I116" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J116" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J116" s="15"/>
       <c r="K116" s="11"/>
       <c r="L116" s="11"/>
       <c r="M116" s="11"/>
@@ -4334,13 +4357,10 @@
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
       <c r="I117" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J117" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J117" s="15"/>
       <c r="K117" s="11"/>
       <c r="L117" s="11"/>
       <c r="M117" s="11"/>
@@ -4356,13 +4376,10 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J118" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J118" s="15"/>
       <c r="K118" s="11"/>
       <c r="L118" s="11"/>
       <c r="M118" s="11"/>
@@ -4378,13 +4395,10 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J119" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J119" s="15"/>
       <c r="K119" s="11"/>
       <c r="L119" s="11"/>
       <c r="M119" s="11"/>
@@ -4400,13 +4414,10 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J120" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J120" s="15"/>
       <c r="K120" s="11"/>
       <c r="L120" s="11"/>
       <c r="M120" s="11"/>
@@ -4422,13 +4433,10 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J121" s="10" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J121" s="15"/>
       <c r="K121" s="11"/>
       <c r="L121" s="11"/>
       <c r="M121" s="11"/>
@@ -4444,11 +4452,11 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J122" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J122:J133" si="6">IF(I122="","",1440-I122)</f>
         <v/>
       </c>
       <c r="K122" s="11"/>
@@ -4466,11 +4474,11 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J123" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K123" s="11"/>
@@ -4488,11 +4496,11 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J124" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K124" s="11"/>
@@ -4510,11 +4518,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4532,11 +4540,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4554,11 +4562,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4576,11 +4584,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4598,11 +4606,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4620,11 +4628,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4642,11 +4650,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4664,11 +4672,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4686,11 +4694,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4708,11 +4716,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B133:F133,H134)=0,"",SUM(B133:F133,H134))</f>
+        <f t="shared" ref="I134:I197" si="7">IF(SUM(B133:F133,H134)=0,"",SUM(B133:F133,H134))</f>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="8">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4730,11 +4738,11 @@
       <c r="G135" s="9"/>
       <c r="H135" s="9"/>
       <c r="I135" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J135" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K135" s="11"/>
@@ -4752,11 +4760,11 @@
       <c r="G136" s="9"/>
       <c r="H136" s="9"/>
       <c r="I136" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J136" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K136" s="11"/>
@@ -4774,11 +4782,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4796,11 +4804,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4818,11 +4826,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4840,11 +4848,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4862,11 +4870,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4884,11 +4892,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4906,11 +4914,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4928,11 +4936,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -4950,11 +4958,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -4972,11 +4980,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -4994,11 +5002,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5016,11 +5024,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5038,11 +5046,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5060,11 +5068,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5082,11 +5090,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5104,11 +5112,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5126,11 +5134,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5148,11 +5156,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5170,11 +5178,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5192,11 +5200,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5214,11 +5222,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5236,11 +5244,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5258,11 +5266,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5280,11 +5288,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5302,11 +5310,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5324,11 +5332,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5346,11 +5354,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5368,11 +5376,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5390,11 +5398,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5412,11 +5420,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5434,11 +5442,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5456,11 +5464,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5478,11 +5486,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5500,11 +5508,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5522,11 +5530,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5544,11 +5552,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5566,11 +5574,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5588,11 +5596,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5610,11 +5618,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5632,11 +5640,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5654,11 +5662,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5676,11 +5684,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5698,11 +5706,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5720,11 +5728,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5742,11 +5750,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5764,11 +5772,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5786,11 +5794,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5808,11 +5816,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5830,11 +5838,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5852,11 +5860,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5874,11 +5882,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5896,11 +5904,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5918,11 +5926,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5940,11 +5948,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -5962,11 +5970,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -5984,11 +5992,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6006,11 +6014,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6028,11 +6036,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6050,11 +6058,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6072,11 +6080,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6094,11 +6102,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6116,11 +6124,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B197:F197,H198)=0,"",SUM(B197:F197,H198))</f>
+        <f t="shared" ref="I198:I261" si="9">IF(SUM(B197:F197,H198)=0,"",SUM(B197:F197,H198))</f>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="10">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6138,11 +6146,11 @@
       <c r="G199" s="9"/>
       <c r="H199" s="9"/>
       <c r="I199" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J199" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K199" s="11"/>
@@ -6160,11 +6168,11 @@
       <c r="G200" s="9"/>
       <c r="H200" s="9"/>
       <c r="I200" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J200" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K200" s="11"/>
@@ -6182,11 +6190,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6204,11 +6212,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6226,11 +6234,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6248,11 +6256,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6270,11 +6278,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6292,11 +6300,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6314,11 +6322,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6336,11 +6344,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6358,11 +6366,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6380,11 +6388,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6402,11 +6410,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6424,11 +6432,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6446,11 +6454,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6468,11 +6476,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6490,11 +6498,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6512,11 +6520,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6534,11 +6542,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6556,11 +6564,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6578,11 +6586,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6600,11 +6608,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6622,11 +6630,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6644,11 +6652,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6666,11 +6674,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6688,11 +6696,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6710,11 +6718,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6732,11 +6740,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6754,11 +6762,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6776,11 +6784,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6798,11 +6806,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6820,11 +6828,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6842,11 +6850,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6864,11 +6872,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6886,11 +6894,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6908,11 +6916,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6930,11 +6938,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -6952,11 +6960,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -6974,11 +6982,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -6996,11 +7004,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7018,11 +7026,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7040,11 +7048,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7062,11 +7070,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7084,11 +7092,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7106,11 +7114,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7128,11 +7136,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7150,11 +7158,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7172,11 +7180,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7194,11 +7202,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7216,11 +7224,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7238,11 +7246,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7260,11 +7268,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7282,11 +7290,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7304,11 +7312,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7326,11 +7334,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7348,11 +7356,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7370,11 +7378,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7392,11 +7400,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7414,11 +7422,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7436,11 +7444,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7458,11 +7466,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7480,11 +7488,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7502,11 +7510,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7524,11 +7532,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B261:F261,H262)=0,"",SUM(B261:F261,H262))</f>
+        <f t="shared" ref="I262:I325" si="11">IF(SUM(B261:F261,H262)=0,"",SUM(B261:F261,H262))</f>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="12">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7546,11 +7554,11 @@
       <c r="G263" s="9"/>
       <c r="H263" s="9"/>
       <c r="I263" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J263" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K263" s="11"/>
@@ -7568,11 +7576,11 @@
       <c r="G264" s="9"/>
       <c r="H264" s="9"/>
       <c r="I264" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J264" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K264" s="11"/>
@@ -7590,11 +7598,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7612,11 +7620,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7634,11 +7642,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7656,11 +7664,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7678,11 +7686,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7700,11 +7708,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7722,11 +7730,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7744,11 +7752,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7766,11 +7774,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7788,11 +7796,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7810,11 +7818,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7832,11 +7840,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7854,11 +7862,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7876,11 +7884,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7898,11 +7906,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7920,11 +7928,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7942,11 +7950,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -7964,11 +7972,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -7986,11 +7994,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8008,11 +8016,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8030,11 +8038,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8052,11 +8060,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8074,11 +8082,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8096,11 +8104,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8118,11 +8126,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8140,11 +8148,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8162,11 +8170,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8184,11 +8192,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8206,11 +8214,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8228,11 +8236,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8250,11 +8258,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8272,11 +8280,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8294,11 +8302,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8316,11 +8324,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8338,11 +8346,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8360,11 +8368,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8382,11 +8390,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8404,11 +8412,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8426,11 +8434,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8448,11 +8456,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8470,11 +8478,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8492,11 +8500,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8514,11 +8522,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8536,11 +8544,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8558,11 +8566,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8580,11 +8588,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8602,11 +8610,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8624,11 +8632,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8646,11 +8654,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8668,11 +8676,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8690,11 +8698,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8712,11 +8720,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8734,11 +8742,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8756,11 +8764,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8778,11 +8786,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8800,11 +8808,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8822,11 +8830,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8844,11 +8852,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8866,11 +8874,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8888,11 +8896,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8910,11 +8918,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8932,11 +8940,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B325:F325,H326)=0,"",SUM(B325:F325,H326))</f>
+        <f t="shared" ref="I326:I389" si="13">IF(SUM(B325:F325,H326)=0,"",SUM(B325:F325,H326))</f>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="14">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -8954,11 +8962,11 @@
       <c r="G327" s="9"/>
       <c r="H327" s="9"/>
       <c r="I327" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J327" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K327" s="11"/>
@@ -8976,11 +8984,11 @@
       <c r="G328" s="9"/>
       <c r="H328" s="9"/>
       <c r="I328" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J328" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K328" s="11"/>
@@ -8998,11 +9006,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9020,11 +9028,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9042,11 +9050,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9064,11 +9072,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9086,11 +9094,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9108,11 +9116,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9130,11 +9138,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9152,11 +9160,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9174,11 +9182,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9196,11 +9204,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9218,11 +9226,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9240,11 +9248,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9262,11 +9270,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9284,11 +9292,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9306,11 +9314,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9328,11 +9336,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9350,11 +9358,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9372,11 +9380,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9394,11 +9402,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9416,11 +9424,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9438,11 +9446,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9460,11 +9468,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9482,11 +9490,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9504,11 +9512,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9526,11 +9534,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9548,11 +9556,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9570,11 +9578,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9592,11 +9600,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9614,11 +9622,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9636,11 +9644,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9658,11 +9666,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9680,11 +9688,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9702,11 +9710,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9724,11 +9732,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9746,11 +9754,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9768,11 +9776,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9790,11 +9798,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9812,11 +9820,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9834,11 +9842,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9856,11 +9864,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9878,11 +9886,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9900,11 +9908,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9922,11 +9930,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -9944,11 +9952,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -9966,11 +9974,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -9988,11 +9996,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10010,11 +10018,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10032,11 +10040,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10054,11 +10062,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10076,11 +10084,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10098,11 +10106,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10120,11 +10128,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10142,11 +10150,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10164,11 +10172,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10186,11 +10194,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10208,11 +10216,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10230,11 +10238,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10252,11 +10260,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10274,11 +10282,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10296,11 +10304,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10318,11 +10326,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10340,11 +10348,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B389:F389,H390)=0,"",SUM(B389:F389,H390))</f>
+        <f t="shared" ref="I390:I401" si="15">IF(SUM(B389:F389,H390)=0,"",SUM(B389:F389,H390))</f>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="16">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10362,11 +10370,11 @@
       <c r="G391" s="9"/>
       <c r="H391" s="9"/>
       <c r="I391" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J391" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K391" s="11"/>
@@ -10384,11 +10392,11 @@
       <c r="G392" s="9"/>
       <c r="H392" s="9"/>
       <c r="I392" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J392" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K392" s="11"/>
@@ -10406,11 +10414,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10428,11 +10436,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10450,11 +10458,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10472,11 +10480,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10494,11 +10502,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10516,11 +10524,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10538,11 +10546,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10560,11 +10568,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10581,11 +10589,11 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K401" s="11"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130404EB-D143-41EE-B00E-58D8CF597E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2682,26 +2682,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B41" s="9">
+        <v>300</v>
+      </c>
+      <c r="C41" s="9">
+        <v>140</v>
+      </c>
+      <c r="D41" s="9">
+        <v>150</v>
+      </c>
+      <c r="E41" s="9">
+        <v>60</v>
+      </c>
+      <c r="F41" s="9">
+        <v>300</v>
+      </c>
+      <c r="G41" s="9">
+        <v>5</v>
+      </c>
+      <c r="H41" s="9">
+        <v>180</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="12"/>
+        <v>310</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="12" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{833D6AB8-B41D-4997-8BBA-DA8605328FC5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2728,26 +2728,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B42" s="9">
+        <v>210</v>
+      </c>
+      <c r="C42" s="9">
+        <v>130</v>
+      </c>
+      <c r="D42" s="9">
+        <v>70</v>
+      </c>
+      <c r="E42" s="9">
+        <v>60</v>
+      </c>
+      <c r="F42" s="9">
+        <v>350</v>
+      </c>
+      <c r="G42" s="9">
+        <v>7</v>
+      </c>
+      <c r="H42" s="9">
+        <v>180</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" ref="I42:I70" si="2">IF(SUM(B42:F42,H42)=0," ",SUM(B42:F42,H42))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="12"/>
+        <v>440</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{833D6AB8-B41D-4997-8BBA-DA8605328FC5}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E1E7A19-8908-4E12-AFB5-1EE3BA59D16F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t xml:space="preserve">relaxed day </t>
+  </si>
+  <si>
+    <t>low</t>
   </si>
 </sst>
 </file>
@@ -943,7 +946,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N404"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1073,7 +1076,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
-        <v>46254</v>
+        <v>46251</v>
       </c>
       <c r="B6" s="14">
         <v>370</v>
@@ -1118,149 +1121,149 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>46255</v>
-      </c>
-      <c r="B7" s="9">
-        <v>320</v>
-      </c>
-      <c r="C7" s="9">
+      <c r="A7" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="14">
+        <v>300</v>
+      </c>
+      <c r="C7" s="15">
         <v>20</v>
       </c>
-      <c r="D7" s="9">
-        <v>30</v>
-      </c>
-      <c r="E7" s="9">
-        <v>30</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="D7" s="15">
+        <v>80</v>
+      </c>
+      <c r="E7" s="15">
+        <v>70</v>
+      </c>
+      <c r="F7" s="15">
         <v>350</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="15">
         <v>7</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="15">
+        <v>70</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" ref="I7:I12" si="0">IF(SUM(B7:F7,H7)=0," ",SUM(B7:F7,H7))</f>
+        <v>890</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" ref="J7:J13" si="1">IF(I7=" ","",1440-I7)</f>
+        <v>550</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B8" s="14">
+        <v>350</v>
+      </c>
+      <c r="C8" s="15">
+        <v>50</v>
+      </c>
+      <c r="D8" s="15">
         <v>80</v>
       </c>
-      <c r="I7" s="15">
-        <f t="shared" ref="I7:I41" si="0">IF(SUM(B7:F7,H7)=0," ",SUM(B7:F7,H7))</f>
-        <v>830</v>
-      </c>
-      <c r="J7" s="15">
-        <f t="shared" ref="J7:J70" si="1">IF(I7=" ","",1440-I7)</f>
-        <v>610</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <v>46256</v>
-      </c>
-      <c r="B8" s="9">
+      <c r="E8" s="15">
+        <v>60</v>
+      </c>
+      <c r="F8" s="15">
         <v>350</v>
       </c>
-      <c r="C8" s="9">
-        <v>20</v>
-      </c>
-      <c r="D8" s="9">
-        <v>50</v>
-      </c>
-      <c r="E8" s="9">
-        <v>50</v>
-      </c>
-      <c r="F8" s="9">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>50</v>
+      <c r="G8" s="15">
+        <v>7</v>
+      </c>
+      <c r="H8" s="15">
+        <v>90</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>520</v>
+        <v>980</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>920</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L8" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B9" s="14">
+        <v>270</v>
+      </c>
+      <c r="C9" s="15">
+        <v>50</v>
+      </c>
+      <c r="D9" s="15">
         <v>60</v>
       </c>
-      <c r="M8" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <v>46257</v>
-      </c>
-      <c r="B9" s="9">
-        <v>340</v>
-      </c>
-      <c r="C9" s="9">
-        <v>20</v>
-      </c>
-      <c r="D9" s="9">
-        <v>30</v>
-      </c>
-      <c r="E9" s="9">
-        <v>40</v>
-      </c>
-      <c r="F9" s="9">
-        <v>0</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9">
+      <c r="E9" s="15">
         <v>60</v>
+      </c>
+      <c r="F9" s="15">
+        <v>200</v>
+      </c>
+      <c r="G9" s="15">
+        <v>4</v>
+      </c>
+      <c r="H9" s="15">
+        <v>80</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>490</v>
+        <v>720</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>950</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="11" t="s">
+        <v>720</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M9" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>63</v>
+      <c r="M9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="B10" s="9">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="C10" s="9">
         <v>20</v>
@@ -1272,271 +1275,271 @@
         <v>30</v>
       </c>
       <c r="F10" s="9">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G10" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H10" s="9">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>610</v>
+        <v>830</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>830</v>
+        <v>610</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N10" s="12" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
-        <v>46259</v>
+        <v>46256</v>
       </c>
       <c r="B11" s="9">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="C11" s="9">
         <v>20</v>
       </c>
       <c r="D11" s="9">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E11" s="9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F11" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G11" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>715</v>
+        <v>520</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>725</v>
+        <v>920</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="N11" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="8">
-        <v>46260</v>
+        <v>46257</v>
       </c>
       <c r="B12" s="9">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="C12" s="9">
+        <v>20</v>
+      </c>
+      <c r="D12" s="9">
         <v>30</v>
-      </c>
-      <c r="D12" s="9">
-        <v>40</v>
       </c>
       <c r="E12" s="9">
         <v>40</v>
       </c>
       <c r="F12" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G12" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H12" s="9">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>740</v>
+        <v>490</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>700</v>
+        <v>950</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>59</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>61</v>
       </c>
       <c r="N12" s="12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
-        <v>46261</v>
+        <v>46258</v>
       </c>
       <c r="B13" s="9">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="C13" s="9">
         <v>20</v>
       </c>
       <c r="D13" s="9">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E13" s="9">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F13" s="9">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G13" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H13" s="9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="0"/>
-        <v>810</v>
+        <f t="shared" ref="I13:I44" si="2">IF(SUM(B13:F13,H13)=0," ",SUM(B13:F13,H13))</f>
+        <v>610</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>830</v>
       </c>
       <c r="K13" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B14" s="9">
+        <v>300</v>
+      </c>
+      <c r="C14" s="9">
+        <v>20</v>
+      </c>
+      <c r="D14" s="9">
+        <v>45</v>
+      </c>
+      <c r="E14" s="9">
+        <v>40</v>
+      </c>
+      <c r="F14" s="9">
+        <v>250</v>
+      </c>
+      <c r="G14" s="9">
+        <v>5</v>
+      </c>
+      <c r="H14" s="9">
+        <v>60</v>
+      </c>
+      <c r="I14" s="15">
+        <f t="shared" si="2"/>
+        <v>715</v>
+      </c>
+      <c r="J14" s="15">
+        <f t="shared" ref="J14:J73" si="3">IF(I14=" ","",1440-I14)</f>
+        <v>725</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L14" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" s="12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="9">
-        <v>390</v>
-      </c>
-      <c r="C14" s="9">
-        <v>30</v>
-      </c>
-      <c r="D14" s="9">
-        <v>40</v>
-      </c>
-      <c r="E14" s="9">
-        <v>50</v>
-      </c>
-      <c r="F14" s="9">
-        <v>200</v>
-      </c>
-      <c r="G14" s="9">
-        <v>4</v>
-      </c>
-      <c r="H14" s="9">
-        <v>70</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>780</v>
-      </c>
-      <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>660</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" s="11" t="s">
-        <v>57</v>
-      </c>
       <c r="M14" s="11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="N14" s="12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
-        <v>46263</v>
+        <v>46260</v>
       </c>
       <c r="B15" s="9">
-        <v>480</v>
+        <v>310</v>
       </c>
       <c r="C15" s="9">
         <v>30</v>
       </c>
       <c r="D15" s="9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E15" s="9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F15" s="9">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G15" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H15" s="9">
         <v>70</v>
       </c>
       <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>660</v>
+        <f t="shared" si="2"/>
+        <v>740</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>780</v>
+        <f t="shared" si="3"/>
+        <v>700</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>59</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>61</v>
       </c>
       <c r="N15" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
-        <v>46264</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="9">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="C16" s="9">
         <v>20</v>
@@ -1548,159 +1551,159 @@
         <v>50</v>
       </c>
       <c r="F16" s="9">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G16" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H16" s="9">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="0"/>
-        <v>500</v>
+        <f t="shared" si="2"/>
+        <v>810</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>940</v>
+        <f t="shared" si="3"/>
+        <v>630</v>
       </c>
       <c r="K16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="9">
+        <v>390</v>
+      </c>
+      <c r="C17" s="9">
+        <v>30</v>
+      </c>
+      <c r="D17" s="9">
+        <v>40</v>
+      </c>
+      <c r="E17" s="9">
+        <v>50</v>
+      </c>
+      <c r="F17" s="9">
+        <v>200</v>
+      </c>
+      <c r="G17" s="9">
+        <v>4</v>
+      </c>
+      <c r="H17" s="9">
+        <v>70</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" si="2"/>
+        <v>780</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="3"/>
+        <v>660</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M17" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="L16" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="N16" s="12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
-        <v>46265</v>
-      </c>
-      <c r="B17" s="9">
-        <v>360</v>
-      </c>
-      <c r="C17" s="9">
-        <v>20</v>
-      </c>
-      <c r="D17" s="9">
-        <v>60</v>
-      </c>
-      <c r="E17" s="9">
-        <v>60</v>
-      </c>
-      <c r="F17" s="9">
-        <v>100</v>
-      </c>
-      <c r="G17" s="9">
-        <v>2</v>
-      </c>
-      <c r="H17" s="9">
-        <v>90</v>
-      </c>
-      <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>690</v>
-      </c>
-      <c r="J17" s="15">
-        <f t="shared" si="1"/>
-        <v>750</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L17" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M17" s="11" t="s">
-        <v>51</v>
-      </c>
       <c r="N17" s="12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
-        <v>46266</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="9">
         <v>480</v>
       </c>
       <c r="C18" s="9">
+        <v>30</v>
+      </c>
+      <c r="D18" s="9">
         <v>50</v>
       </c>
-      <c r="D18" s="9">
+      <c r="E18" s="9">
+        <v>30</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>70</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="2"/>
+        <v>660</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="3"/>
+        <v>780</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L18" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="9">
-        <v>60</v>
-      </c>
-      <c r="F18" s="9">
-        <v>250</v>
-      </c>
-      <c r="G18" s="9">
-        <v>5</v>
-      </c>
-      <c r="H18" s="9">
-        <v>80</v>
-      </c>
-      <c r="I18" s="15">
-        <f t="shared" si="0"/>
-        <v>980</v>
-      </c>
-      <c r="J18" s="15">
-        <f t="shared" si="1"/>
-        <v>460</v>
-      </c>
-      <c r="K18" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="L18" s="11" t="s">
-        <v>57</v>
-      </c>
       <c r="M18" s="11" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N18" s="12" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
-        <v>46267</v>
+        <v>46264</v>
       </c>
       <c r="B19" s="9">
         <v>300</v>
       </c>
       <c r="C19" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D19" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E19" s="9">
         <v>50</v>
       </c>
       <c r="F19" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G19" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H19" s="9">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I19" s="15">
-        <f t="shared" si="0"/>
-        <v>770</v>
+        <f t="shared" si="2"/>
+        <v>500</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="1"/>
-        <v>670</v>
+        <f t="shared" si="3"/>
+        <v>940</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>58</v>
@@ -1712,70 +1715,70 @@
         <v>58</v>
       </c>
       <c r="N19" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="B20" s="9">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="C20" s="9">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D20" s="9">
+        <v>60</v>
+      </c>
+      <c r="E20" s="9">
+        <v>60</v>
+      </c>
+      <c r="F20" s="9">
+        <v>100</v>
+      </c>
+      <c r="G20" s="9">
+        <v>2</v>
+      </c>
+      <c r="H20" s="9">
+        <v>90</v>
+      </c>
+      <c r="I20" s="15">
+        <f t="shared" si="2"/>
+        <v>690</v>
+      </c>
+      <c r="J20" s="15">
+        <f t="shared" si="3"/>
+        <v>750</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="E20" s="9">
-        <v>80</v>
-      </c>
-      <c r="F20" s="9">
-        <v>300</v>
-      </c>
-      <c r="G20" s="9">
-        <v>6</v>
-      </c>
-      <c r="H20" s="9">
-        <v>80</v>
-      </c>
-      <c r="I20" s="15">
-        <f t="shared" si="0"/>
-        <v>820</v>
-      </c>
-      <c r="J20" s="15">
-        <f t="shared" si="1"/>
-        <v>620</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="M20" s="11" t="s">
         <v>51</v>
       </c>
       <c r="N20" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="B21" s="9">
         <v>480</v>
       </c>
       <c r="C21" s="9">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="D21" s="9">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E21" s="9">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F21" s="9">
         <v>250</v>
@@ -1784,110 +1787,110 @@
         <v>5</v>
       </c>
       <c r="H21" s="9">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I21" s="15">
-        <f t="shared" si="0"/>
-        <v>1060</v>
+        <f t="shared" si="2"/>
+        <v>980</v>
       </c>
       <c r="J21" s="15">
-        <f t="shared" si="1"/>
-        <v>380</v>
+        <f t="shared" si="3"/>
+        <v>460</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L21" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B22" s="9">
+        <v>300</v>
+      </c>
+      <c r="C22" s="9">
+        <v>40</v>
+      </c>
+      <c r="D22" s="9">
         <v>60</v>
       </c>
-      <c r="M21" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N21" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
-        <v>46270</v>
-      </c>
-      <c r="B22" s="9">
-        <v>360</v>
-      </c>
-      <c r="C22" s="9">
-        <v>90</v>
-      </c>
-      <c r="D22" s="9">
+      <c r="E22" s="9">
         <v>50</v>
       </c>
-      <c r="E22" s="9">
-        <v>80</v>
-      </c>
       <c r="F22" s="9">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G22" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22" s="9">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I22" s="15">
-        <f t="shared" si="0"/>
-        <v>660</v>
+        <f t="shared" si="2"/>
+        <v>770</v>
       </c>
       <c r="J22" s="15">
-        <f t="shared" si="1"/>
-        <v>780</v>
+        <f t="shared" si="3"/>
+        <v>670</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>58</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>58</v>
       </c>
       <c r="N22" s="12" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
-        <v>46271</v>
+        <v>46268</v>
       </c>
       <c r="B23" s="9">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="C23" s="9">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D23" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E23" s="9">
         <v>80</v>
       </c>
       <c r="F23" s="9">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G23" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H23" s="9">
         <v>80</v>
       </c>
       <c r="I23" s="15">
-        <f t="shared" si="0"/>
-        <v>480</v>
+        <f t="shared" si="2"/>
+        <v>820</v>
       </c>
       <c r="J23" s="15">
-        <f t="shared" si="1"/>
-        <v>960</v>
+        <f t="shared" si="3"/>
+        <v>620</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L23" s="11" t="s">
         <v>57</v>
@@ -1896,409 +1899,409 @@
         <v>51</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B24" s="9">
         <v>480</v>
       </c>
       <c r="C24" s="9">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D24" s="9">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="E24" s="9">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="F24" s="9">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G24" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H24" s="9">
         <v>90</v>
       </c>
       <c r="I24" s="15">
-        <f t="shared" si="0"/>
-        <v>1200</v>
+        <f t="shared" si="2"/>
+        <v>1060</v>
       </c>
       <c r="J24" s="15">
-        <f t="shared" si="1"/>
-        <v>240</v>
+        <f t="shared" si="3"/>
+        <v>380</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
-        <v>46273</v>
+        <v>46270</v>
       </c>
       <c r="B25" s="9">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C25" s="9">
         <v>90</v>
       </c>
       <c r="D25" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E25" s="9">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F25" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G25" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H25" s="9">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I25" s="15">
-        <f t="shared" si="0"/>
-        <v>860</v>
+        <f t="shared" si="2"/>
+        <v>660</v>
       </c>
       <c r="J25" s="15">
-        <f t="shared" si="1"/>
-        <v>580</v>
+        <f t="shared" si="3"/>
+        <v>780</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
-        <v>46274</v>
+        <v>46271</v>
       </c>
       <c r="B26" s="9">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="C26" s="9">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D26" s="9">
+        <v>60</v>
+      </c>
+      <c r="E26" s="9">
         <v>80</v>
       </c>
-      <c r="E26" s="9">
-        <v>70</v>
-      </c>
       <c r="F26" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G26" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H26" s="9">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" si="0"/>
-        <v>990</v>
+        <f t="shared" si="2"/>
+        <v>480</v>
       </c>
       <c r="J26" s="15">
-        <f t="shared" si="1"/>
-        <v>450</v>
+        <f t="shared" si="3"/>
+        <v>960</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>49</v>
       </c>
       <c r="L26" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B27" s="9">
+        <v>480</v>
+      </c>
+      <c r="C27" s="9">
+        <v>90</v>
+      </c>
+      <c r="D27" s="9">
+        <v>120</v>
+      </c>
+      <c r="E27" s="9">
+        <v>120</v>
+      </c>
+      <c r="F27" s="9">
+        <v>300</v>
+      </c>
+      <c r="G27" s="9">
+        <v>6</v>
+      </c>
+      <c r="H27" s="9">
+        <v>90</v>
+      </c>
+      <c r="I27" s="15">
+        <f t="shared" si="2"/>
+        <v>1200</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" si="3"/>
+        <v>240</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M26" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
-        <v>46275</v>
-      </c>
-      <c r="B27" s="9">
-        <v>300</v>
-      </c>
-      <c r="C27" s="9">
-        <v>100</v>
-      </c>
-      <c r="D27" s="9">
-        <v>70</v>
-      </c>
-      <c r="E27" s="9">
-        <v>60</v>
-      </c>
-      <c r="F27" s="9">
-        <v>100</v>
-      </c>
-      <c r="G27" s="9">
-        <v>2</v>
-      </c>
-      <c r="H27" s="9">
-        <v>120</v>
-      </c>
-      <c r="I27" s="15">
-        <f t="shared" si="0"/>
-        <v>750</v>
-      </c>
-      <c r="J27" s="15">
-        <f t="shared" si="1"/>
-        <v>690</v>
-      </c>
-      <c r="K27" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L27" s="11" t="s">
-        <v>60</v>
-      </c>
       <c r="M27" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="B28" s="9">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C28" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D28" s="9">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E28" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F28" s="9">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G28" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="9">
         <v>120</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="0"/>
-        <v>1040</v>
+        <f t="shared" si="2"/>
+        <v>860</v>
       </c>
       <c r="J28" s="15">
-        <f t="shared" si="1"/>
-        <v>400</v>
+        <f t="shared" si="3"/>
+        <v>580</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N28" s="12" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
-        <v>46277</v>
+        <v>46274</v>
       </c>
       <c r="B29" s="9">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C29" s="9">
         <v>100</v>
       </c>
       <c r="D29" s="9">
+        <v>80</v>
+      </c>
+      <c r="E29" s="9">
+        <v>70</v>
+      </c>
+      <c r="F29" s="9">
+        <v>250</v>
+      </c>
+      <c r="G29" s="9">
+        <v>5</v>
+      </c>
+      <c r="H29" s="9">
+        <v>130</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="E29" s="9">
-        <v>50</v>
-      </c>
-      <c r="F29" s="9">
-        <v>0</v>
-      </c>
-      <c r="G29" s="9">
-        <v>0</v>
-      </c>
-      <c r="H29" s="9">
-        <v>300</v>
-      </c>
-      <c r="I29" s="15">
-        <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
-      <c r="J29" s="15">
-        <f t="shared" si="1"/>
-        <v>640</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>60</v>
       </c>
       <c r="M29" s="11" t="s">
         <v>61</v>
       </c>
       <c r="N29" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
-        <v>46278</v>
+        <v>46275</v>
       </c>
       <c r="B30" s="9">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="C30" s="9">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D30" s="9">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E30" s="9">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F30" s="9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G30" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" s="9">
         <v>120</v>
       </c>
       <c r="I30" s="15">
-        <f t="shared" si="0"/>
-        <v>470</v>
+        <f t="shared" si="2"/>
+        <v>750</v>
       </c>
       <c r="J30" s="15">
-        <f t="shared" si="1"/>
-        <v>970</v>
+        <f t="shared" si="3"/>
+        <v>690</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="B31" s="9">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="C31" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D31" s="9">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E31" s="9">
         <v>60</v>
       </c>
       <c r="F31" s="9">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G31" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H31" s="9">
         <v>120</v>
       </c>
       <c r="I31" s="15">
-        <f t="shared" si="0"/>
-        <v>810</v>
+        <f t="shared" si="2"/>
+        <v>1040</v>
       </c>
       <c r="J31" s="15">
-        <f t="shared" si="1"/>
-        <v>630</v>
+        <f t="shared" si="3"/>
+        <v>400</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
-        <v>46280</v>
+        <v>46277</v>
       </c>
       <c r="B32" s="9">
         <v>300</v>
       </c>
       <c r="C32" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D32" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E32" s="9">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F32" s="9">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G32" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" s="9">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="I32" s="15">
-        <f t="shared" si="0"/>
-        <v>960</v>
+        <f t="shared" si="2"/>
+        <v>800</v>
       </c>
       <c r="J32" s="15">
-        <f t="shared" si="1"/>
-        <v>480</v>
+        <f t="shared" si="3"/>
+        <v>640</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>59</v>
@@ -2310,47 +2313,47 @@
         <v>61</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
-        <v>46281</v>
+        <v>46278</v>
       </c>
       <c r="B33" s="9">
         <v>240</v>
       </c>
       <c r="C33" s="9">
+        <v>30</v>
+      </c>
+      <c r="D33" s="9">
+        <v>40</v>
+      </c>
+      <c r="E33" s="9">
+        <v>40</v>
+      </c>
+      <c r="F33" s="9">
+        <v>0</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9">
         <v>120</v>
       </c>
-      <c r="D33" s="9">
-        <v>80</v>
-      </c>
-      <c r="E33" s="9">
-        <v>70</v>
-      </c>
-      <c r="F33" s="9">
-        <v>150</v>
-      </c>
-      <c r="G33" s="9">
-        <v>3</v>
-      </c>
-      <c r="H33" s="9">
-        <v>150</v>
-      </c>
       <c r="I33" s="15">
-        <f t="shared" si="0"/>
-        <v>810</v>
+        <f t="shared" si="2"/>
+        <v>470</v>
       </c>
       <c r="J33" s="15">
-        <f t="shared" si="1"/>
-        <v>630</v>
+        <f t="shared" si="3"/>
+        <v>970</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M33" s="11" t="s">
         <v>51</v>
@@ -2361,10 +2364,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="B34" s="9">
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="C34" s="9">
         <v>120</v>
@@ -2373,27 +2376,27 @@
         <v>70</v>
       </c>
       <c r="E34" s="9">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F34" s="9">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G34" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H34" s="9">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="I34" s="15">
-        <f t="shared" si="0"/>
-        <v>1030</v>
+        <f t="shared" si="2"/>
+        <v>810</v>
       </c>
       <c r="J34" s="15">
-        <f t="shared" si="1"/>
-        <v>410</v>
+        <f t="shared" si="3"/>
+        <v>630</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L34" s="11" t="s">
         <v>60</v>
@@ -2402,41 +2405,41 @@
         <v>61</v>
       </c>
       <c r="N34" s="12" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B35" s="9">
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="C35" s="9">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D35" s="9">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E35" s="9">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F35" s="9">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G35" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H35" s="9">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="I35" s="15">
-        <f t="shared" si="0"/>
-        <v>1120</v>
+        <f t="shared" si="2"/>
+        <v>960</v>
       </c>
       <c r="J35" s="15">
-        <f t="shared" si="1"/>
-        <v>320</v>
+        <f t="shared" si="3"/>
+        <v>480</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>59</v>
@@ -2445,182 +2448,182 @@
         <v>60</v>
       </c>
       <c r="M35" s="11" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="N35" s="12" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
-        <v>46284</v>
+        <v>46281</v>
       </c>
       <c r="B36" s="9">
-        <v>420</v>
+        <v>240</v>
       </c>
       <c r="C36" s="9">
         <v>120</v>
       </c>
       <c r="D36" s="9">
+        <v>80</v>
+      </c>
+      <c r="E36" s="9">
         <v>70</v>
       </c>
-      <c r="E36" s="9">
-        <v>40</v>
-      </c>
       <c r="F36" s="9">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G36" s="9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H36" s="9">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="I36" s="15">
-        <f t="shared" si="0"/>
-        <v>780</v>
+        <f t="shared" si="2"/>
+        <v>810</v>
       </c>
       <c r="J36" s="15">
-        <f t="shared" si="1"/>
-        <v>660</v>
+        <f t="shared" si="3"/>
+        <v>630</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="8">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="B37" s="9">
         <v>300</v>
       </c>
       <c r="C37" s="9">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D37" s="9">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="E37" s="9">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F37" s="9">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G37" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H37" s="9">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="I37" s="15">
-        <f t="shared" si="0"/>
-        <v>630</v>
+        <f t="shared" si="2"/>
+        <v>1030</v>
       </c>
       <c r="J37" s="15">
-        <f t="shared" si="1"/>
-        <v>810</v>
+        <f t="shared" si="3"/>
+        <v>410</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M37" s="11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="N37" s="12" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="8">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="B38" s="9">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="C38" s="9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D38" s="9">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E38" s="9">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F38" s="9">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G38" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H38" s="9">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="I38" s="15">
-        <f t="shared" si="0"/>
-        <v>880</v>
+        <f t="shared" si="2"/>
+        <v>1120</v>
       </c>
       <c r="J38" s="15">
-        <f t="shared" si="1"/>
-        <v>560</v>
+        <f t="shared" si="3"/>
+        <v>320</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="N38" s="12" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="8">
-        <v>46287</v>
+        <v>46284</v>
       </c>
       <c r="B39" s="9">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="C39" s="9">
+        <v>120</v>
+      </c>
+      <c r="D39" s="9">
+        <v>70</v>
+      </c>
+      <c r="E39" s="9">
+        <v>40</v>
+      </c>
+      <c r="F39" s="9">
+        <v>0</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9">
         <v>130</v>
       </c>
-      <c r="D39" s="9">
-        <v>80</v>
-      </c>
-      <c r="E39" s="9">
-        <v>90</v>
-      </c>
-      <c r="F39" s="9">
-        <v>250</v>
-      </c>
-      <c r="G39" s="9">
-        <v>5</v>
-      </c>
-      <c r="H39" s="9">
-        <v>120</v>
-      </c>
       <c r="I39" s="15">
-        <f t="shared" si="0"/>
-        <v>970</v>
+        <f t="shared" si="2"/>
+        <v>780</v>
       </c>
       <c r="J39" s="15">
-        <f t="shared" si="1"/>
-        <v>470</v>
+        <f t="shared" si="3"/>
+        <v>660</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>59</v>
@@ -2629,96 +2632,96 @@
         <v>60</v>
       </c>
       <c r="M39" s="11" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="N39" s="12" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="8">
-        <v>46288</v>
+        <v>46285</v>
       </c>
       <c r="B40" s="9">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="C40" s="9">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="D40" s="9">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="E40" s="9">
+        <v>0</v>
+      </c>
+      <c r="F40" s="9">
+        <v>0</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
+        <v>180</v>
+      </c>
+      <c r="I40" s="15">
+        <f t="shared" si="2"/>
+        <v>630</v>
+      </c>
+      <c r="J40" s="15">
+        <f t="shared" si="3"/>
+        <v>810</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="L40" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F40" s="9">
-        <v>200</v>
-      </c>
-      <c r="G40" s="9">
-        <v>4</v>
-      </c>
-      <c r="H40" s="9">
-        <v>150</v>
-      </c>
-      <c r="I40" s="15">
-        <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
-      <c r="J40" s="15">
-        <f t="shared" si="1"/>
-        <v>540</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L40" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="M40" s="11" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B41" s="9">
         <v>300</v>
       </c>
       <c r="C41" s="9">
+        <v>120</v>
+      </c>
+      <c r="D41" s="9">
+        <v>50</v>
+      </c>
+      <c r="E41" s="9">
+        <v>70</v>
+      </c>
+      <c r="F41" s="9">
+        <v>200</v>
+      </c>
+      <c r="G41" s="9">
+        <v>4</v>
+      </c>
+      <c r="H41" s="9">
         <v>140</v>
       </c>
-      <c r="D41" s="9">
-        <v>150</v>
-      </c>
-      <c r="E41" s="9">
-        <v>60</v>
-      </c>
-      <c r="F41" s="9">
-        <v>300</v>
-      </c>
-      <c r="G41" s="9">
-        <v>5</v>
-      </c>
-      <c r="H41" s="9">
-        <v>180</v>
-      </c>
       <c r="I41" s="15">
-        <f t="shared" si="0"/>
-        <v>1130</v>
+        <f t="shared" si="2"/>
+        <v>880</v>
       </c>
       <c r="J41" s="15">
-        <f t="shared" si="1"/>
-        <v>310</v>
+        <f t="shared" si="3"/>
+        <v>560</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>49</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="M41" s="11" t="s">
         <v>51</v>
@@ -2729,137 +2732,233 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
-        <v>46290</v>
+        <v>46287</v>
       </c>
       <c r="B42" s="9">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="C42" s="9">
         <v>130</v>
       </c>
       <c r="D42" s="9">
+        <v>80</v>
+      </c>
+      <c r="E42" s="9">
+        <v>90</v>
+      </c>
+      <c r="F42" s="9">
+        <v>250</v>
+      </c>
+      <c r="G42" s="9">
+        <v>5</v>
+      </c>
+      <c r="H42" s="9">
+        <v>120</v>
+      </c>
+      <c r="I42" s="15">
+        <f t="shared" si="2"/>
+        <v>970</v>
+      </c>
+      <c r="J42" s="15">
+        <f t="shared" si="3"/>
+        <v>470</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M42" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N42" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A43" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="9">
+        <v>270</v>
+      </c>
+      <c r="C43" s="9">
+        <v>130</v>
+      </c>
+      <c r="D43" s="9">
+        <v>80</v>
+      </c>
+      <c r="E43" s="9">
         <v>70</v>
       </c>
-      <c r="E42" s="9">
+      <c r="F43" s="9">
+        <v>200</v>
+      </c>
+      <c r="G43" s="9">
+        <v>4</v>
+      </c>
+      <c r="H43" s="9">
+        <v>150</v>
+      </c>
+      <c r="I43" s="15">
+        <f t="shared" si="2"/>
+        <v>900</v>
+      </c>
+      <c r="J43" s="15">
+        <f t="shared" si="3"/>
+        <v>540</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="M43" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A44" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="9">
+        <v>300</v>
+      </c>
+      <c r="C44" s="9">
+        <v>140</v>
+      </c>
+      <c r="D44" s="9">
+        <v>150</v>
+      </c>
+      <c r="E44" s="9">
         <v>60</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F44" s="9">
+        <v>300</v>
+      </c>
+      <c r="G44" s="9">
+        <v>5</v>
+      </c>
+      <c r="H44" s="9">
+        <v>180</v>
+      </c>
+      <c r="I44" s="15">
+        <f t="shared" si="2"/>
+        <v>1130</v>
+      </c>
+      <c r="J44" s="15">
+        <f t="shared" si="3"/>
+        <v>310</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="12" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A45" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B45" s="9">
+        <v>210</v>
+      </c>
+      <c r="C45" s="9">
+        <v>130</v>
+      </c>
+      <c r="D45" s="9">
+        <v>70</v>
+      </c>
+      <c r="E45" s="9">
+        <v>60</v>
+      </c>
+      <c r="F45" s="9">
         <v>350</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G45" s="9">
         <v>7</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H45" s="9">
         <v>180</v>
       </c>
-      <c r="I42" s="15">
-        <f t="shared" ref="I42:I70" si="2">IF(SUM(B42:F42,H42)=0," ",SUM(B42:F42,H42))</f>
+      <c r="I45" s="15">
+        <f t="shared" ref="I45:I73" si="4">IF(SUM(B45:F45,H45)=0," ",SUM(B45:F45,H45))</f>
         <v>1000</v>
       </c>
-      <c r="J42" s="15">
-        <f t="shared" si="1"/>
+      <c r="J45" s="15">
+        <f t="shared" si="3"/>
         <v>440</v>
       </c>
-      <c r="K42" s="11" t="s">
+      <c r="K45" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="L42" s="11" t="s">
+      <c r="L45" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="M42" s="11" t="s">
+      <c r="M45" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N42" s="12" t="s">
+      <c r="N45" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="12"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="12"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="12"/>
-    </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="12"/>
+      <c r="A46" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B46" s="9">
+        <v>210</v>
+      </c>
+      <c r="C46" s="9">
+        <v>160</v>
+      </c>
+      <c r="D46" s="9">
+        <v>70</v>
+      </c>
+      <c r="E46" s="9">
+        <v>90</v>
+      </c>
+      <c r="F46" s="9">
+        <v>0</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
+        <v>190</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" si="4"/>
+        <v>720</v>
+      </c>
+      <c r="J46" s="15">
+        <f t="shared" si="3"/>
+        <v>720</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L46" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M46" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N46" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
@@ -2871,11 +2970,11 @@
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K47" s="11"/>
@@ -2893,11 +2992,11 @@
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J48" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K48" s="11"/>
@@ -2915,11 +3014,11 @@
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J49" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K49" s="11"/>
@@ -2937,11 +3036,11 @@
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K50" s="11"/>
@@ -2959,11 +3058,11 @@
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
       <c r="I51" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J51" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K51" s="11"/>
@@ -2981,11 +3080,11 @@
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
       <c r="I52" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J52" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K52" s="11"/>
@@ -3003,11 +3102,11 @@
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
       <c r="I53" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J53" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K53" s="11"/>
@@ -3025,11 +3124,11 @@
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
       <c r="I54" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J54" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K54" s="11"/>
@@ -3047,11 +3146,11 @@
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
       <c r="I55" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J55" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K55" s="11"/>
@@ -3069,11 +3168,11 @@
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
       <c r="I56" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J56" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K56" s="11"/>
@@ -3091,11 +3190,11 @@
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
       <c r="I57" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J57" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K57" s="11"/>
@@ -3113,11 +3212,11 @@
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
       <c r="I58" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J58" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K58" s="11"/>
@@ -3135,11 +3234,11 @@
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
       <c r="I59" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J59" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K59" s="11"/>
@@ -3157,11 +3256,11 @@
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
       <c r="I60" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J60" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K60" s="11"/>
@@ -3179,11 +3278,11 @@
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
       <c r="I61" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J61" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K61" s="11"/>
@@ -3201,11 +3300,11 @@
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
       <c r="I62" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J62" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K62" s="11"/>
@@ -3223,11 +3322,11 @@
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
       <c r="I63" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K63" s="11"/>
@@ -3245,11 +3344,11 @@
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
       <c r="I64" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K64" s="11"/>
@@ -3267,11 +3366,11 @@
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K65" s="11"/>
@@ -3289,11 +3388,11 @@
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J66" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K66" s="11"/>
@@ -3311,11 +3410,11 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
       <c r="I67" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J67" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K67" s="11"/>
@@ -3333,11 +3432,11 @@
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
       <c r="I68" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K68" s="11"/>
@@ -3355,11 +3454,11 @@
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K69" s="11"/>
@@ -3377,11 +3476,11 @@
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K70" s="11"/>
@@ -3399,11 +3498,11 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" ref="I71:I114" si="3">IF(SUM(B71:F71,H71)=0," ",SUM(B71:F71,H71))</f>
+        <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" ref="J71:J114" si="4">IF(I71=" ","",1440-I71)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="11"/>
@@ -3421,11 +3520,11 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J72" s="15" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J72" s="15" t="str">
-        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K72" s="11"/>
@@ -3443,11 +3542,11 @@
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
       <c r="I73" s="15" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J73" s="15" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J73" s="15" t="str">
-        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="K73" s="11"/>
@@ -3465,11 +3564,11 @@
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="I74:I117" si="5">IF(SUM(B74:F74,H74)=0," ",SUM(B74:F74,H74))</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="J74:J117" si="6">IF(I74=" ","",1440-I74)</f>
         <v/>
       </c>
       <c r="K74" s="11"/>
@@ -3487,11 +3586,11 @@
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K75" s="11"/>
@@ -3509,11 +3608,11 @@
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K76" s="11"/>
@@ -3531,11 +3630,11 @@
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K77" s="11"/>
@@ -3553,11 +3652,11 @@
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K78" s="11"/>
@@ -3575,11 +3674,11 @@
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K79" s="11"/>
@@ -3597,11 +3696,11 @@
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K80" s="11"/>
@@ -3619,11 +3718,11 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K81" s="11"/>
@@ -3641,11 +3740,11 @@
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K82" s="11"/>
@@ -3663,11 +3762,11 @@
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K83" s="11"/>
@@ -3685,11 +3784,11 @@
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K84" s="11"/>
@@ -3707,11 +3806,11 @@
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K85" s="11"/>
@@ -3729,11 +3828,11 @@
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K86" s="11"/>
@@ -3751,11 +3850,11 @@
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K87" s="11"/>
@@ -3773,11 +3872,11 @@
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K88" s="11"/>
@@ -3795,11 +3894,11 @@
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K89" s="11"/>
@@ -3817,11 +3916,11 @@
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K90" s="11"/>
@@ -3839,11 +3938,11 @@
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K91" s="11"/>
@@ -3861,11 +3960,11 @@
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K92" s="11"/>
@@ -3883,11 +3982,11 @@
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K93" s="11"/>
@@ -3905,11 +4004,11 @@
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K94" s="11"/>
@@ -3927,11 +4026,11 @@
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K95" s="11"/>
@@ -3949,11 +4048,11 @@
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K96" s="11"/>
@@ -3971,11 +4070,11 @@
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K97" s="11"/>
@@ -3993,11 +4092,11 @@
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K98" s="11"/>
@@ -4015,11 +4114,11 @@
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K99" s="11"/>
@@ -4037,11 +4136,11 @@
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K100" s="11"/>
@@ -4059,11 +4158,11 @@
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K101" s="11"/>
@@ -4081,11 +4180,11 @@
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K102" s="11"/>
@@ -4103,11 +4202,11 @@
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K103" s="11"/>
@@ -4125,11 +4224,11 @@
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K104" s="11"/>
@@ -4147,11 +4246,11 @@
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K105" s="11"/>
@@ -4169,11 +4268,11 @@
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K106" s="11"/>
@@ -4191,11 +4290,11 @@
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K107" s="11"/>
@@ -4213,11 +4312,11 @@
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K108" s="11"/>
@@ -4235,11 +4334,11 @@
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K109" s="11"/>
@@ -4257,11 +4356,11 @@
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K110" s="11"/>
@@ -4279,11 +4378,11 @@
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K111" s="11"/>
@@ -4301,11 +4400,11 @@
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K112" s="11"/>
@@ -4323,11 +4422,11 @@
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K113" s="11"/>
@@ -4345,11 +4444,11 @@
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="K114" s="11"/>
@@ -4366,11 +4465,14 @@
       <c r="F115" s="9"/>
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
-      <c r="I115" s="10" t="str">
-        <f t="shared" ref="I115:I133" si="5">IF(SUM(B114:F114,H115)=0,"",SUM(B114:F114,H115))</f>
-        <v/>
-      </c>
-      <c r="J115" s="15"/>
+      <c r="I115" s="15" t="str">
+        <f t="shared" si="5"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J115" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K115" s="11"/>
       <c r="L115" s="11"/>
       <c r="M115" s="11"/>
@@ -4385,11 +4487,14 @@
       <c r="F116" s="9"/>
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
-      <c r="I116" s="10" t="str">
+      <c r="I116" s="15" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J116" s="15"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J116" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K116" s="11"/>
       <c r="L116" s="11"/>
       <c r="M116" s="11"/>
@@ -4404,11 +4509,14 @@
       <c r="F117" s="9"/>
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
-      <c r="I117" s="10" t="str">
+      <c r="I117" s="15" t="str">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J117" s="15"/>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="J117" s="15" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K117" s="11"/>
       <c r="L117" s="11"/>
       <c r="M117" s="11"/>
@@ -4424,7 +4532,7 @@
       <c r="G118" s="9"/>
       <c r="H118" s="9"/>
       <c r="I118" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="I118:I136" si="7">IF(SUM(B117:F117,H118)=0,"",SUM(B117:F117,H118))</f>
         <v/>
       </c>
       <c r="J118" s="15"/>
@@ -4443,7 +4551,7 @@
       <c r="G119" s="9"/>
       <c r="H119" s="9"/>
       <c r="I119" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J119" s="15"/>
@@ -4462,7 +4570,7 @@
       <c r="G120" s="9"/>
       <c r="H120" s="9"/>
       <c r="I120" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J120" s="15"/>
@@ -4481,7 +4589,7 @@
       <c r="G121" s="9"/>
       <c r="H121" s="9"/>
       <c r="I121" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J121" s="15"/>
@@ -4500,13 +4608,10 @@
       <c r="G122" s="9"/>
       <c r="H122" s="9"/>
       <c r="I122" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J122" s="10" t="str">
-        <f t="shared" ref="J122:J133" si="6">IF(I122="","",1440-I122)</f>
-        <v/>
-      </c>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="J122" s="15"/>
       <c r="K122" s="11"/>
       <c r="L122" s="11"/>
       <c r="M122" s="11"/>
@@ -4522,13 +4627,10 @@
       <c r="G123" s="9"/>
       <c r="H123" s="9"/>
       <c r="I123" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J123" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="J123" s="15"/>
       <c r="K123" s="11"/>
       <c r="L123" s="11"/>
       <c r="M123" s="11"/>
@@ -4544,13 +4646,10 @@
       <c r="G124" s="9"/>
       <c r="H124" s="9"/>
       <c r="I124" s="10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="J124" s="10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="J124" s="15"/>
       <c r="K124" s="11"/>
       <c r="L124" s="11"/>
       <c r="M124" s="11"/>
@@ -4566,11 +4665,11 @@
       <c r="G125" s="9"/>
       <c r="H125" s="9"/>
       <c r="I125" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J125" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J125:J136" si="8">IF(I125="","",1440-I125)</f>
         <v/>
       </c>
       <c r="K125" s="11"/>
@@ -4588,11 +4687,11 @@
       <c r="G126" s="9"/>
       <c r="H126" s="9"/>
       <c r="I126" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J126" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K126" s="11"/>
@@ -4610,11 +4709,11 @@
       <c r="G127" s="9"/>
       <c r="H127" s="9"/>
       <c r="I127" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J127" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K127" s="11"/>
@@ -4632,11 +4731,11 @@
       <c r="G128" s="9"/>
       <c r="H128" s="9"/>
       <c r="I128" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J128" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K128" s="11"/>
@@ -4654,11 +4753,11 @@
       <c r="G129" s="9"/>
       <c r="H129" s="9"/>
       <c r="I129" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J129" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K129" s="11"/>
@@ -4676,11 +4775,11 @@
       <c r="G130" s="9"/>
       <c r="H130" s="9"/>
       <c r="I130" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J130" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K130" s="11"/>
@@ -4698,11 +4797,11 @@
       <c r="G131" s="9"/>
       <c r="H131" s="9"/>
       <c r="I131" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J131" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K131" s="11"/>
@@ -4720,11 +4819,11 @@
       <c r="G132" s="9"/>
       <c r="H132" s="9"/>
       <c r="I132" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J132" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K132" s="11"/>
@@ -4742,11 +4841,11 @@
       <c r="G133" s="9"/>
       <c r="H133" s="9"/>
       <c r="I133" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J133" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K133" s="11"/>
@@ -4764,11 +4863,11 @@
       <c r="G134" s="9"/>
       <c r="H134" s="9"/>
       <c r="I134" s="10" t="str">
-        <f t="shared" ref="I134:I197" si="7">IF(SUM(B133:F133,H134)=0,"",SUM(B133:F133,H134))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J134" s="10" t="str">
-        <f t="shared" ref="J134:J197" si="8">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="K134" s="11"/>
@@ -4830,11 +4929,11 @@
       <c r="G137" s="9"/>
       <c r="H137" s="9"/>
       <c r="I137" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="I137:I200" si="9">IF(SUM(B136:F136,H137)=0,"",SUM(B136:F136,H137))</f>
         <v/>
       </c>
       <c r="J137" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="J137:J200" si="10">IF(I137="","",1440-I137)</f>
         <v/>
       </c>
       <c r="K137" s="11"/>
@@ -4852,11 +4951,11 @@
       <c r="G138" s="9"/>
       <c r="H138" s="9"/>
       <c r="I138" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J138" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K138" s="11"/>
@@ -4874,11 +4973,11 @@
       <c r="G139" s="9"/>
       <c r="H139" s="9"/>
       <c r="I139" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J139" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K139" s="11"/>
@@ -4896,11 +4995,11 @@
       <c r="G140" s="9"/>
       <c r="H140" s="9"/>
       <c r="I140" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J140" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K140" s="11"/>
@@ -4918,11 +5017,11 @@
       <c r="G141" s="9"/>
       <c r="H141" s="9"/>
       <c r="I141" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J141" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K141" s="11"/>
@@ -4940,11 +5039,11 @@
       <c r="G142" s="9"/>
       <c r="H142" s="9"/>
       <c r="I142" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J142" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K142" s="11"/>
@@ -4962,11 +5061,11 @@
       <c r="G143" s="9"/>
       <c r="H143" s="9"/>
       <c r="I143" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J143" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K143" s="11"/>
@@ -4984,11 +5083,11 @@
       <c r="G144" s="9"/>
       <c r="H144" s="9"/>
       <c r="I144" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J144" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K144" s="11"/>
@@ -5006,11 +5105,11 @@
       <c r="G145" s="9"/>
       <c r="H145" s="9"/>
       <c r="I145" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J145" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K145" s="11"/>
@@ -5028,11 +5127,11 @@
       <c r="G146" s="9"/>
       <c r="H146" s="9"/>
       <c r="I146" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J146" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K146" s="11"/>
@@ -5050,11 +5149,11 @@
       <c r="G147" s="9"/>
       <c r="H147" s="9"/>
       <c r="I147" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J147" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K147" s="11"/>
@@ -5072,11 +5171,11 @@
       <c r="G148" s="9"/>
       <c r="H148" s="9"/>
       <c r="I148" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J148" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K148" s="11"/>
@@ -5094,11 +5193,11 @@
       <c r="G149" s="9"/>
       <c r="H149" s="9"/>
       <c r="I149" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J149" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K149" s="11"/>
@@ -5116,11 +5215,11 @@
       <c r="G150" s="9"/>
       <c r="H150" s="9"/>
       <c r="I150" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J150" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K150" s="11"/>
@@ -5138,11 +5237,11 @@
       <c r="G151" s="9"/>
       <c r="H151" s="9"/>
       <c r="I151" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J151" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K151" s="11"/>
@@ -5160,11 +5259,11 @@
       <c r="G152" s="9"/>
       <c r="H152" s="9"/>
       <c r="I152" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J152" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K152" s="11"/>
@@ -5182,11 +5281,11 @@
       <c r="G153" s="9"/>
       <c r="H153" s="9"/>
       <c r="I153" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J153" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K153" s="11"/>
@@ -5204,11 +5303,11 @@
       <c r="G154" s="9"/>
       <c r="H154" s="9"/>
       <c r="I154" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J154" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K154" s="11"/>
@@ -5226,11 +5325,11 @@
       <c r="G155" s="9"/>
       <c r="H155" s="9"/>
       <c r="I155" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J155" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K155" s="11"/>
@@ -5248,11 +5347,11 @@
       <c r="G156" s="9"/>
       <c r="H156" s="9"/>
       <c r="I156" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J156" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K156" s="11"/>
@@ -5270,11 +5369,11 @@
       <c r="G157" s="9"/>
       <c r="H157" s="9"/>
       <c r="I157" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J157" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K157" s="11"/>
@@ -5292,11 +5391,11 @@
       <c r="G158" s="9"/>
       <c r="H158" s="9"/>
       <c r="I158" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J158" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K158" s="11"/>
@@ -5314,11 +5413,11 @@
       <c r="G159" s="9"/>
       <c r="H159" s="9"/>
       <c r="I159" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J159" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K159" s="11"/>
@@ -5336,11 +5435,11 @@
       <c r="G160" s="9"/>
       <c r="H160" s="9"/>
       <c r="I160" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J160" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K160" s="11"/>
@@ -5358,11 +5457,11 @@
       <c r="G161" s="9"/>
       <c r="H161" s="9"/>
       <c r="I161" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J161" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K161" s="11"/>
@@ -5380,11 +5479,11 @@
       <c r="G162" s="9"/>
       <c r="H162" s="9"/>
       <c r="I162" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J162" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K162" s="11"/>
@@ -5402,11 +5501,11 @@
       <c r="G163" s="9"/>
       <c r="H163" s="9"/>
       <c r="I163" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J163" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K163" s="11"/>
@@ -5424,11 +5523,11 @@
       <c r="G164" s="9"/>
       <c r="H164" s="9"/>
       <c r="I164" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J164" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K164" s="11"/>
@@ -5446,11 +5545,11 @@
       <c r="G165" s="9"/>
       <c r="H165" s="9"/>
       <c r="I165" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J165" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K165" s="11"/>
@@ -5468,11 +5567,11 @@
       <c r="G166" s="9"/>
       <c r="H166" s="9"/>
       <c r="I166" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J166" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K166" s="11"/>
@@ -5490,11 +5589,11 @@
       <c r="G167" s="9"/>
       <c r="H167" s="9"/>
       <c r="I167" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J167" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K167" s="11"/>
@@ -5512,11 +5611,11 @@
       <c r="G168" s="9"/>
       <c r="H168" s="9"/>
       <c r="I168" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J168" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K168" s="11"/>
@@ -5534,11 +5633,11 @@
       <c r="G169" s="9"/>
       <c r="H169" s="9"/>
       <c r="I169" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J169" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K169" s="11"/>
@@ -5556,11 +5655,11 @@
       <c r="G170" s="9"/>
       <c r="H170" s="9"/>
       <c r="I170" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J170" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K170" s="11"/>
@@ -5578,11 +5677,11 @@
       <c r="G171" s="9"/>
       <c r="H171" s="9"/>
       <c r="I171" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J171" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K171" s="11"/>
@@ -5600,11 +5699,11 @@
       <c r="G172" s="9"/>
       <c r="H172" s="9"/>
       <c r="I172" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J172" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K172" s="11"/>
@@ -5622,11 +5721,11 @@
       <c r="G173" s="9"/>
       <c r="H173" s="9"/>
       <c r="I173" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J173" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K173" s="11"/>
@@ -5644,11 +5743,11 @@
       <c r="G174" s="9"/>
       <c r="H174" s="9"/>
       <c r="I174" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J174" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K174" s="11"/>
@@ -5666,11 +5765,11 @@
       <c r="G175" s="9"/>
       <c r="H175" s="9"/>
       <c r="I175" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J175" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K175" s="11"/>
@@ -5688,11 +5787,11 @@
       <c r="G176" s="9"/>
       <c r="H176" s="9"/>
       <c r="I176" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J176" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K176" s="11"/>
@@ -5710,11 +5809,11 @@
       <c r="G177" s="9"/>
       <c r="H177" s="9"/>
       <c r="I177" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J177" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K177" s="11"/>
@@ -5732,11 +5831,11 @@
       <c r="G178" s="9"/>
       <c r="H178" s="9"/>
       <c r="I178" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J178" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K178" s="11"/>
@@ -5754,11 +5853,11 @@
       <c r="G179" s="9"/>
       <c r="H179" s="9"/>
       <c r="I179" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J179" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K179" s="11"/>
@@ -5776,11 +5875,11 @@
       <c r="G180" s="9"/>
       <c r="H180" s="9"/>
       <c r="I180" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J180" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K180" s="11"/>
@@ -5798,11 +5897,11 @@
       <c r="G181" s="9"/>
       <c r="H181" s="9"/>
       <c r="I181" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J181" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K181" s="11"/>
@@ -5820,11 +5919,11 @@
       <c r="G182" s="9"/>
       <c r="H182" s="9"/>
       <c r="I182" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J182" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K182" s="11"/>
@@ -5842,11 +5941,11 @@
       <c r="G183" s="9"/>
       <c r="H183" s="9"/>
       <c r="I183" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J183" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K183" s="11"/>
@@ -5864,11 +5963,11 @@
       <c r="G184" s="9"/>
       <c r="H184" s="9"/>
       <c r="I184" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J184" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K184" s="11"/>
@@ -5886,11 +5985,11 @@
       <c r="G185" s="9"/>
       <c r="H185" s="9"/>
       <c r="I185" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J185" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K185" s="11"/>
@@ -5908,11 +6007,11 @@
       <c r="G186" s="9"/>
       <c r="H186" s="9"/>
       <c r="I186" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J186" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K186" s="11"/>
@@ -5930,11 +6029,11 @@
       <c r="G187" s="9"/>
       <c r="H187" s="9"/>
       <c r="I187" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J187" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K187" s="11"/>
@@ -5952,11 +6051,11 @@
       <c r="G188" s="9"/>
       <c r="H188" s="9"/>
       <c r="I188" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J188" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K188" s="11"/>
@@ -5974,11 +6073,11 @@
       <c r="G189" s="9"/>
       <c r="H189" s="9"/>
       <c r="I189" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J189" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K189" s="11"/>
@@ -5996,11 +6095,11 @@
       <c r="G190" s="9"/>
       <c r="H190" s="9"/>
       <c r="I190" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J190" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K190" s="11"/>
@@ -6018,11 +6117,11 @@
       <c r="G191" s="9"/>
       <c r="H191" s="9"/>
       <c r="I191" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J191" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K191" s="11"/>
@@ -6040,11 +6139,11 @@
       <c r="G192" s="9"/>
       <c r="H192" s="9"/>
       <c r="I192" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J192" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K192" s="11"/>
@@ -6062,11 +6161,11 @@
       <c r="G193" s="9"/>
       <c r="H193" s="9"/>
       <c r="I193" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J193" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K193" s="11"/>
@@ -6084,11 +6183,11 @@
       <c r="G194" s="9"/>
       <c r="H194" s="9"/>
       <c r="I194" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J194" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K194" s="11"/>
@@ -6106,11 +6205,11 @@
       <c r="G195" s="9"/>
       <c r="H195" s="9"/>
       <c r="I195" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J195" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K195" s="11"/>
@@ -6128,11 +6227,11 @@
       <c r="G196" s="9"/>
       <c r="H196" s="9"/>
       <c r="I196" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J196" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K196" s="11"/>
@@ -6150,11 +6249,11 @@
       <c r="G197" s="9"/>
       <c r="H197" s="9"/>
       <c r="I197" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J197" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K197" s="11"/>
@@ -6172,11 +6271,11 @@
       <c r="G198" s="9"/>
       <c r="H198" s="9"/>
       <c r="I198" s="10" t="str">
-        <f t="shared" ref="I198:I261" si="9">IF(SUM(B197:F197,H198)=0,"",SUM(B197:F197,H198))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="J198" s="10" t="str">
-        <f t="shared" ref="J198:J261" si="10">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="K198" s="11"/>
@@ -6238,11 +6337,11 @@
       <c r="G201" s="9"/>
       <c r="H201" s="9"/>
       <c r="I201" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="I201:I264" si="11">IF(SUM(B200:F200,H201)=0,"",SUM(B200:F200,H201))</f>
         <v/>
       </c>
       <c r="J201" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="J201:J264" si="12">IF(I201="","",1440-I201)</f>
         <v/>
       </c>
       <c r="K201" s="11"/>
@@ -6260,11 +6359,11 @@
       <c r="G202" s="9"/>
       <c r="H202" s="9"/>
       <c r="I202" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J202" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K202" s="11"/>
@@ -6282,11 +6381,11 @@
       <c r="G203" s="9"/>
       <c r="H203" s="9"/>
       <c r="I203" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J203" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K203" s="11"/>
@@ -6304,11 +6403,11 @@
       <c r="G204" s="9"/>
       <c r="H204" s="9"/>
       <c r="I204" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J204" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K204" s="11"/>
@@ -6326,11 +6425,11 @@
       <c r="G205" s="9"/>
       <c r="H205" s="9"/>
       <c r="I205" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J205" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K205" s="11"/>
@@ -6348,11 +6447,11 @@
       <c r="G206" s="9"/>
       <c r="H206" s="9"/>
       <c r="I206" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J206" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K206" s="11"/>
@@ -6370,11 +6469,11 @@
       <c r="G207" s="9"/>
       <c r="H207" s="9"/>
       <c r="I207" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J207" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K207" s="11"/>
@@ -6392,11 +6491,11 @@
       <c r="G208" s="9"/>
       <c r="H208" s="9"/>
       <c r="I208" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J208" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K208" s="11"/>
@@ -6414,11 +6513,11 @@
       <c r="G209" s="9"/>
       <c r="H209" s="9"/>
       <c r="I209" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J209" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K209" s="11"/>
@@ -6436,11 +6535,11 @@
       <c r="G210" s="9"/>
       <c r="H210" s="9"/>
       <c r="I210" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J210" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K210" s="11"/>
@@ -6458,11 +6557,11 @@
       <c r="G211" s="9"/>
       <c r="H211" s="9"/>
       <c r="I211" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J211" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K211" s="11"/>
@@ -6480,11 +6579,11 @@
       <c r="G212" s="9"/>
       <c r="H212" s="9"/>
       <c r="I212" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J212" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K212" s="11"/>
@@ -6502,11 +6601,11 @@
       <c r="G213" s="9"/>
       <c r="H213" s="9"/>
       <c r="I213" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J213" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K213" s="11"/>
@@ -6524,11 +6623,11 @@
       <c r="G214" s="9"/>
       <c r="H214" s="9"/>
       <c r="I214" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J214" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K214" s="11"/>
@@ -6546,11 +6645,11 @@
       <c r="G215" s="9"/>
       <c r="H215" s="9"/>
       <c r="I215" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J215" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K215" s="11"/>
@@ -6568,11 +6667,11 @@
       <c r="G216" s="9"/>
       <c r="H216" s="9"/>
       <c r="I216" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J216" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K216" s="11"/>
@@ -6590,11 +6689,11 @@
       <c r="G217" s="9"/>
       <c r="H217" s="9"/>
       <c r="I217" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J217" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K217" s="11"/>
@@ -6612,11 +6711,11 @@
       <c r="G218" s="9"/>
       <c r="H218" s="9"/>
       <c r="I218" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J218" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K218" s="11"/>
@@ -6634,11 +6733,11 @@
       <c r="G219" s="9"/>
       <c r="H219" s="9"/>
       <c r="I219" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J219" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K219" s="11"/>
@@ -6656,11 +6755,11 @@
       <c r="G220" s="9"/>
       <c r="H220" s="9"/>
       <c r="I220" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J220" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K220" s="11"/>
@@ -6678,11 +6777,11 @@
       <c r="G221" s="9"/>
       <c r="H221" s="9"/>
       <c r="I221" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J221" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K221" s="11"/>
@@ -6700,11 +6799,11 @@
       <c r="G222" s="9"/>
       <c r="H222" s="9"/>
       <c r="I222" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J222" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K222" s="11"/>
@@ -6722,11 +6821,11 @@
       <c r="G223" s="9"/>
       <c r="H223" s="9"/>
       <c r="I223" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J223" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K223" s="11"/>
@@ -6744,11 +6843,11 @@
       <c r="G224" s="9"/>
       <c r="H224" s="9"/>
       <c r="I224" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J224" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K224" s="11"/>
@@ -6766,11 +6865,11 @@
       <c r="G225" s="9"/>
       <c r="H225" s="9"/>
       <c r="I225" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J225" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K225" s="11"/>
@@ -6788,11 +6887,11 @@
       <c r="G226" s="9"/>
       <c r="H226" s="9"/>
       <c r="I226" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J226" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K226" s="11"/>
@@ -6810,11 +6909,11 @@
       <c r="G227" s="9"/>
       <c r="H227" s="9"/>
       <c r="I227" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J227" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K227" s="11"/>
@@ -6832,11 +6931,11 @@
       <c r="G228" s="9"/>
       <c r="H228" s="9"/>
       <c r="I228" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J228" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K228" s="11"/>
@@ -6854,11 +6953,11 @@
       <c r="G229" s="9"/>
       <c r="H229" s="9"/>
       <c r="I229" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J229" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K229" s="11"/>
@@ -6876,11 +6975,11 @@
       <c r="G230" s="9"/>
       <c r="H230" s="9"/>
       <c r="I230" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J230" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K230" s="11"/>
@@ -6898,11 +6997,11 @@
       <c r="G231" s="9"/>
       <c r="H231" s="9"/>
       <c r="I231" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J231" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K231" s="11"/>
@@ -6920,11 +7019,11 @@
       <c r="G232" s="9"/>
       <c r="H232" s="9"/>
       <c r="I232" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J232" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K232" s="11"/>
@@ -6942,11 +7041,11 @@
       <c r="G233" s="9"/>
       <c r="H233" s="9"/>
       <c r="I233" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J233" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K233" s="11"/>
@@ -6964,11 +7063,11 @@
       <c r="G234" s="9"/>
       <c r="H234" s="9"/>
       <c r="I234" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J234" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K234" s="11"/>
@@ -6986,11 +7085,11 @@
       <c r="G235" s="9"/>
       <c r="H235" s="9"/>
       <c r="I235" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J235" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K235" s="11"/>
@@ -7008,11 +7107,11 @@
       <c r="G236" s="9"/>
       <c r="H236" s="9"/>
       <c r="I236" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J236" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K236" s="11"/>
@@ -7030,11 +7129,11 @@
       <c r="G237" s="9"/>
       <c r="H237" s="9"/>
       <c r="I237" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J237" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K237" s="11"/>
@@ -7052,11 +7151,11 @@
       <c r="G238" s="9"/>
       <c r="H238" s="9"/>
       <c r="I238" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J238" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K238" s="11"/>
@@ -7074,11 +7173,11 @@
       <c r="G239" s="9"/>
       <c r="H239" s="9"/>
       <c r="I239" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J239" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K239" s="11"/>
@@ -7096,11 +7195,11 @@
       <c r="G240" s="9"/>
       <c r="H240" s="9"/>
       <c r="I240" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J240" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K240" s="11"/>
@@ -7118,11 +7217,11 @@
       <c r="G241" s="9"/>
       <c r="H241" s="9"/>
       <c r="I241" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J241" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K241" s="11"/>
@@ -7140,11 +7239,11 @@
       <c r="G242" s="9"/>
       <c r="H242" s="9"/>
       <c r="I242" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J242" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K242" s="11"/>
@@ -7162,11 +7261,11 @@
       <c r="G243" s="9"/>
       <c r="H243" s="9"/>
       <c r="I243" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J243" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K243" s="11"/>
@@ -7184,11 +7283,11 @@
       <c r="G244" s="9"/>
       <c r="H244" s="9"/>
       <c r="I244" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J244" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K244" s="11"/>
@@ -7206,11 +7305,11 @@
       <c r="G245" s="9"/>
       <c r="H245" s="9"/>
       <c r="I245" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J245" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K245" s="11"/>
@@ -7228,11 +7327,11 @@
       <c r="G246" s="9"/>
       <c r="H246" s="9"/>
       <c r="I246" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J246" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K246" s="11"/>
@@ -7250,11 +7349,11 @@
       <c r="G247" s="9"/>
       <c r="H247" s="9"/>
       <c r="I247" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J247" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K247" s="11"/>
@@ -7272,11 +7371,11 @@
       <c r="G248" s="9"/>
       <c r="H248" s="9"/>
       <c r="I248" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J248" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K248" s="11"/>
@@ -7294,11 +7393,11 @@
       <c r="G249" s="9"/>
       <c r="H249" s="9"/>
       <c r="I249" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J249" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K249" s="11"/>
@@ -7316,11 +7415,11 @@
       <c r="G250" s="9"/>
       <c r="H250" s="9"/>
       <c r="I250" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J250" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K250" s="11"/>
@@ -7338,11 +7437,11 @@
       <c r="G251" s="9"/>
       <c r="H251" s="9"/>
       <c r="I251" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J251" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K251" s="11"/>
@@ -7360,11 +7459,11 @@
       <c r="G252" s="9"/>
       <c r="H252" s="9"/>
       <c r="I252" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J252" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K252" s="11"/>
@@ -7382,11 +7481,11 @@
       <c r="G253" s="9"/>
       <c r="H253" s="9"/>
       <c r="I253" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J253" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K253" s="11"/>
@@ -7404,11 +7503,11 @@
       <c r="G254" s="9"/>
       <c r="H254" s="9"/>
       <c r="I254" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J254" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K254" s="11"/>
@@ -7426,11 +7525,11 @@
       <c r="G255" s="9"/>
       <c r="H255" s="9"/>
       <c r="I255" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J255" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K255" s="11"/>
@@ -7448,11 +7547,11 @@
       <c r="G256" s="9"/>
       <c r="H256" s="9"/>
       <c r="I256" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J256" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K256" s="11"/>
@@ -7470,11 +7569,11 @@
       <c r="G257" s="9"/>
       <c r="H257" s="9"/>
       <c r="I257" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J257" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K257" s="11"/>
@@ -7492,11 +7591,11 @@
       <c r="G258" s="9"/>
       <c r="H258" s="9"/>
       <c r="I258" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J258" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K258" s="11"/>
@@ -7514,11 +7613,11 @@
       <c r="G259" s="9"/>
       <c r="H259" s="9"/>
       <c r="I259" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J259" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K259" s="11"/>
@@ -7536,11 +7635,11 @@
       <c r="G260" s="9"/>
       <c r="H260" s="9"/>
       <c r="I260" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J260" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K260" s="11"/>
@@ -7558,11 +7657,11 @@
       <c r="G261" s="9"/>
       <c r="H261" s="9"/>
       <c r="I261" s="10" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J261" s="10" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K261" s="11"/>
@@ -7580,11 +7679,11 @@
       <c r="G262" s="9"/>
       <c r="H262" s="9"/>
       <c r="I262" s="10" t="str">
-        <f t="shared" ref="I262:I325" si="11">IF(SUM(B261:F261,H262)=0,"",SUM(B261:F261,H262))</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J262" s="10" t="str">
-        <f t="shared" ref="J262:J325" si="12">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="K262" s="11"/>
@@ -7646,11 +7745,11 @@
       <c r="G265" s="9"/>
       <c r="H265" s="9"/>
       <c r="I265" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="I265:I328" si="13">IF(SUM(B264:F264,H265)=0,"",SUM(B264:F264,H265))</f>
         <v/>
       </c>
       <c r="J265" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="J265:J328" si="14">IF(I265="","",1440-I265)</f>
         <v/>
       </c>
       <c r="K265" s="11"/>
@@ -7668,11 +7767,11 @@
       <c r="G266" s="9"/>
       <c r="H266" s="9"/>
       <c r="I266" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J266" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K266" s="11"/>
@@ -7690,11 +7789,11 @@
       <c r="G267" s="9"/>
       <c r="H267" s="9"/>
       <c r="I267" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J267" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K267" s="11"/>
@@ -7712,11 +7811,11 @@
       <c r="G268" s="9"/>
       <c r="H268" s="9"/>
       <c r="I268" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J268" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K268" s="11"/>
@@ -7734,11 +7833,11 @@
       <c r="G269" s="9"/>
       <c r="H269" s="9"/>
       <c r="I269" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J269" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K269" s="11"/>
@@ -7756,11 +7855,11 @@
       <c r="G270" s="9"/>
       <c r="H270" s="9"/>
       <c r="I270" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J270" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K270" s="11"/>
@@ -7778,11 +7877,11 @@
       <c r="G271" s="9"/>
       <c r="H271" s="9"/>
       <c r="I271" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J271" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K271" s="11"/>
@@ -7800,11 +7899,11 @@
       <c r="G272" s="9"/>
       <c r="H272" s="9"/>
       <c r="I272" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J272" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K272" s="11"/>
@@ -7822,11 +7921,11 @@
       <c r="G273" s="9"/>
       <c r="H273" s="9"/>
       <c r="I273" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J273" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K273" s="11"/>
@@ -7844,11 +7943,11 @@
       <c r="G274" s="9"/>
       <c r="H274" s="9"/>
       <c r="I274" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J274" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K274" s="11"/>
@@ -7866,11 +7965,11 @@
       <c r="G275" s="9"/>
       <c r="H275" s="9"/>
       <c r="I275" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J275" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K275" s="11"/>
@@ -7888,11 +7987,11 @@
       <c r="G276" s="9"/>
       <c r="H276" s="9"/>
       <c r="I276" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J276" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K276" s="11"/>
@@ -7910,11 +8009,11 @@
       <c r="G277" s="9"/>
       <c r="H277" s="9"/>
       <c r="I277" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J277" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K277" s="11"/>
@@ -7932,11 +8031,11 @@
       <c r="G278" s="9"/>
       <c r="H278" s="9"/>
       <c r="I278" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J278" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K278" s="11"/>
@@ -7954,11 +8053,11 @@
       <c r="G279" s="9"/>
       <c r="H279" s="9"/>
       <c r="I279" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J279" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K279" s="11"/>
@@ -7976,11 +8075,11 @@
       <c r="G280" s="9"/>
       <c r="H280" s="9"/>
       <c r="I280" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J280" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K280" s="11"/>
@@ -7998,11 +8097,11 @@
       <c r="G281" s="9"/>
       <c r="H281" s="9"/>
       <c r="I281" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J281" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K281" s="11"/>
@@ -8020,11 +8119,11 @@
       <c r="G282" s="9"/>
       <c r="H282" s="9"/>
       <c r="I282" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J282" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K282" s="11"/>
@@ -8042,11 +8141,11 @@
       <c r="G283" s="9"/>
       <c r="H283" s="9"/>
       <c r="I283" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J283" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K283" s="11"/>
@@ -8064,11 +8163,11 @@
       <c r="G284" s="9"/>
       <c r="H284" s="9"/>
       <c r="I284" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J284" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K284" s="11"/>
@@ -8086,11 +8185,11 @@
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J285" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K285" s="11"/>
@@ -8108,11 +8207,11 @@
       <c r="G286" s="9"/>
       <c r="H286" s="9"/>
       <c r="I286" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J286" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K286" s="11"/>
@@ -8130,11 +8229,11 @@
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J287" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K287" s="11"/>
@@ -8152,11 +8251,11 @@
       <c r="G288" s="9"/>
       <c r="H288" s="9"/>
       <c r="I288" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J288" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K288" s="11"/>
@@ -8174,11 +8273,11 @@
       <c r="G289" s="9"/>
       <c r="H289" s="9"/>
       <c r="I289" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J289" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K289" s="11"/>
@@ -8196,11 +8295,11 @@
       <c r="G290" s="9"/>
       <c r="H290" s="9"/>
       <c r="I290" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J290" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K290" s="11"/>
@@ -8218,11 +8317,11 @@
       <c r="G291" s="9"/>
       <c r="H291" s="9"/>
       <c r="I291" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J291" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K291" s="11"/>
@@ -8240,11 +8339,11 @@
       <c r="G292" s="9"/>
       <c r="H292" s="9"/>
       <c r="I292" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J292" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K292" s="11"/>
@@ -8262,11 +8361,11 @@
       <c r="G293" s="9"/>
       <c r="H293" s="9"/>
       <c r="I293" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J293" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K293" s="11"/>
@@ -8284,11 +8383,11 @@
       <c r="G294" s="9"/>
       <c r="H294" s="9"/>
       <c r="I294" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J294" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K294" s="11"/>
@@ -8306,11 +8405,11 @@
       <c r="G295" s="9"/>
       <c r="H295" s="9"/>
       <c r="I295" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J295" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K295" s="11"/>
@@ -8328,11 +8427,11 @@
       <c r="G296" s="9"/>
       <c r="H296" s="9"/>
       <c r="I296" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J296" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K296" s="11"/>
@@ -8350,11 +8449,11 @@
       <c r="G297" s="9"/>
       <c r="H297" s="9"/>
       <c r="I297" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J297" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K297" s="11"/>
@@ -8372,11 +8471,11 @@
       <c r="G298" s="9"/>
       <c r="H298" s="9"/>
       <c r="I298" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J298" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K298" s="11"/>
@@ -8394,11 +8493,11 @@
       <c r="G299" s="9"/>
       <c r="H299" s="9"/>
       <c r="I299" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J299" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K299" s="11"/>
@@ -8416,11 +8515,11 @@
       <c r="G300" s="9"/>
       <c r="H300" s="9"/>
       <c r="I300" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J300" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K300" s="11"/>
@@ -8438,11 +8537,11 @@
       <c r="G301" s="9"/>
       <c r="H301" s="9"/>
       <c r="I301" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J301" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K301" s="11"/>
@@ -8460,11 +8559,11 @@
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J302" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K302" s="11"/>
@@ -8482,11 +8581,11 @@
       <c r="G303" s="9"/>
       <c r="H303" s="9"/>
       <c r="I303" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J303" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K303" s="11"/>
@@ -8504,11 +8603,11 @@
       <c r="G304" s="9"/>
       <c r="H304" s="9"/>
       <c r="I304" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J304" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K304" s="11"/>
@@ -8526,11 +8625,11 @@
       <c r="G305" s="9"/>
       <c r="H305" s="9"/>
       <c r="I305" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J305" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K305" s="11"/>
@@ -8548,11 +8647,11 @@
       <c r="G306" s="9"/>
       <c r="H306" s="9"/>
       <c r="I306" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J306" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K306" s="11"/>
@@ -8570,11 +8669,11 @@
       <c r="G307" s="9"/>
       <c r="H307" s="9"/>
       <c r="I307" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J307" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K307" s="11"/>
@@ -8592,11 +8691,11 @@
       <c r="G308" s="9"/>
       <c r="H308" s="9"/>
       <c r="I308" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J308" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K308" s="11"/>
@@ -8614,11 +8713,11 @@
       <c r="G309" s="9"/>
       <c r="H309" s="9"/>
       <c r="I309" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J309" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K309" s="11"/>
@@ -8636,11 +8735,11 @@
       <c r="G310" s="9"/>
       <c r="H310" s="9"/>
       <c r="I310" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J310" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K310" s="11"/>
@@ -8658,11 +8757,11 @@
       <c r="G311" s="9"/>
       <c r="H311" s="9"/>
       <c r="I311" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J311" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K311" s="11"/>
@@ -8680,11 +8779,11 @@
       <c r="G312" s="9"/>
       <c r="H312" s="9"/>
       <c r="I312" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J312" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K312" s="11"/>
@@ -8702,11 +8801,11 @@
       <c r="G313" s="9"/>
       <c r="H313" s="9"/>
       <c r="I313" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J313" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K313" s="11"/>
@@ -8724,11 +8823,11 @@
       <c r="G314" s="9"/>
       <c r="H314" s="9"/>
       <c r="I314" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J314" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K314" s="11"/>
@@ -8746,11 +8845,11 @@
       <c r="G315" s="9"/>
       <c r="H315" s="9"/>
       <c r="I315" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J315" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K315" s="11"/>
@@ -8768,11 +8867,11 @@
       <c r="G316" s="9"/>
       <c r="H316" s="9"/>
       <c r="I316" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J316" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K316" s="11"/>
@@ -8790,11 +8889,11 @@
       <c r="G317" s="9"/>
       <c r="H317" s="9"/>
       <c r="I317" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J317" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K317" s="11"/>
@@ -8812,11 +8911,11 @@
       <c r="G318" s="9"/>
       <c r="H318" s="9"/>
       <c r="I318" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J318" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K318" s="11"/>
@@ -8834,11 +8933,11 @@
       <c r="G319" s="9"/>
       <c r="H319" s="9"/>
       <c r="I319" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J319" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K319" s="11"/>
@@ -8856,11 +8955,11 @@
       <c r="G320" s="9"/>
       <c r="H320" s="9"/>
       <c r="I320" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J320" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K320" s="11"/>
@@ -8878,11 +8977,11 @@
       <c r="G321" s="9"/>
       <c r="H321" s="9"/>
       <c r="I321" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J321" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K321" s="11"/>
@@ -8900,11 +8999,11 @@
       <c r="G322" s="9"/>
       <c r="H322" s="9"/>
       <c r="I322" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J322" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K322" s="11"/>
@@ -8922,11 +9021,11 @@
       <c r="G323" s="9"/>
       <c r="H323" s="9"/>
       <c r="I323" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J323" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K323" s="11"/>
@@ -8944,11 +9043,11 @@
       <c r="G324" s="9"/>
       <c r="H324" s="9"/>
       <c r="I324" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J324" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K324" s="11"/>
@@ -8966,11 +9065,11 @@
       <c r="G325" s="9"/>
       <c r="H325" s="9"/>
       <c r="I325" s="10" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J325" s="10" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K325" s="11"/>
@@ -8988,11 +9087,11 @@
       <c r="G326" s="9"/>
       <c r="H326" s="9"/>
       <c r="I326" s="10" t="str">
-        <f t="shared" ref="I326:I389" si="13">IF(SUM(B325:F325,H326)=0,"",SUM(B325:F325,H326))</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="J326" s="10" t="str">
-        <f t="shared" ref="J326:J389" si="14">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="K326" s="11"/>
@@ -9054,11 +9153,11 @@
       <c r="G329" s="9"/>
       <c r="H329" s="9"/>
       <c r="I329" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="I329:I392" si="15">IF(SUM(B328:F328,H329)=0,"",SUM(B328:F328,H329))</f>
         <v/>
       </c>
       <c r="J329" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="J329:J392" si="16">IF(I329="","",1440-I329)</f>
         <v/>
       </c>
       <c r="K329" s="11"/>
@@ -9076,11 +9175,11 @@
       <c r="G330" s="9"/>
       <c r="H330" s="9"/>
       <c r="I330" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J330" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K330" s="11"/>
@@ -9098,11 +9197,11 @@
       <c r="G331" s="9"/>
       <c r="H331" s="9"/>
       <c r="I331" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J331" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K331" s="11"/>
@@ -9120,11 +9219,11 @@
       <c r="G332" s="9"/>
       <c r="H332" s="9"/>
       <c r="I332" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J332" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K332" s="11"/>
@@ -9142,11 +9241,11 @@
       <c r="G333" s="9"/>
       <c r="H333" s="9"/>
       <c r="I333" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J333" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K333" s="11"/>
@@ -9164,11 +9263,11 @@
       <c r="G334" s="9"/>
       <c r="H334" s="9"/>
       <c r="I334" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J334" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K334" s="11"/>
@@ -9186,11 +9285,11 @@
       <c r="G335" s="9"/>
       <c r="H335" s="9"/>
       <c r="I335" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J335" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K335" s="11"/>
@@ -9208,11 +9307,11 @@
       <c r="G336" s="9"/>
       <c r="H336" s="9"/>
       <c r="I336" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J336" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K336" s="11"/>
@@ -9230,11 +9329,11 @@
       <c r="G337" s="9"/>
       <c r="H337" s="9"/>
       <c r="I337" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J337" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K337" s="11"/>
@@ -9252,11 +9351,11 @@
       <c r="G338" s="9"/>
       <c r="H338" s="9"/>
       <c r="I338" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J338" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K338" s="11"/>
@@ -9274,11 +9373,11 @@
       <c r="G339" s="9"/>
       <c r="H339" s="9"/>
       <c r="I339" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J339" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K339" s="11"/>
@@ -9296,11 +9395,11 @@
       <c r="G340" s="9"/>
       <c r="H340" s="9"/>
       <c r="I340" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J340" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K340" s="11"/>
@@ -9318,11 +9417,11 @@
       <c r="G341" s="9"/>
       <c r="H341" s="9"/>
       <c r="I341" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J341" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K341" s="11"/>
@@ -9340,11 +9439,11 @@
       <c r="G342" s="9"/>
       <c r="H342" s="9"/>
       <c r="I342" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J342" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K342" s="11"/>
@@ -9362,11 +9461,11 @@
       <c r="G343" s="9"/>
       <c r="H343" s="9"/>
       <c r="I343" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J343" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K343" s="11"/>
@@ -9384,11 +9483,11 @@
       <c r="G344" s="9"/>
       <c r="H344" s="9"/>
       <c r="I344" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J344" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K344" s="11"/>
@@ -9406,11 +9505,11 @@
       <c r="G345" s="9"/>
       <c r="H345" s="9"/>
       <c r="I345" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J345" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K345" s="11"/>
@@ -9428,11 +9527,11 @@
       <c r="G346" s="9"/>
       <c r="H346" s="9"/>
       <c r="I346" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J346" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K346" s="11"/>
@@ -9450,11 +9549,11 @@
       <c r="G347" s="9"/>
       <c r="H347" s="9"/>
       <c r="I347" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J347" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K347" s="11"/>
@@ -9472,11 +9571,11 @@
       <c r="G348" s="9"/>
       <c r="H348" s="9"/>
       <c r="I348" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J348" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K348" s="11"/>
@@ -9494,11 +9593,11 @@
       <c r="G349" s="9"/>
       <c r="H349" s="9"/>
       <c r="I349" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J349" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K349" s="11"/>
@@ -9516,11 +9615,11 @@
       <c r="G350" s="9"/>
       <c r="H350" s="9"/>
       <c r="I350" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J350" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K350" s="11"/>
@@ -9538,11 +9637,11 @@
       <c r="G351" s="9"/>
       <c r="H351" s="9"/>
       <c r="I351" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J351" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K351" s="11"/>
@@ -9560,11 +9659,11 @@
       <c r="G352" s="9"/>
       <c r="H352" s="9"/>
       <c r="I352" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J352" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K352" s="11"/>
@@ -9582,11 +9681,11 @@
       <c r="G353" s="9"/>
       <c r="H353" s="9"/>
       <c r="I353" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J353" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K353" s="11"/>
@@ -9604,11 +9703,11 @@
       <c r="G354" s="9"/>
       <c r="H354" s="9"/>
       <c r="I354" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J354" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K354" s="11"/>
@@ -9626,11 +9725,11 @@
       <c r="G355" s="9"/>
       <c r="H355" s="9"/>
       <c r="I355" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J355" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K355" s="11"/>
@@ -9648,11 +9747,11 @@
       <c r="G356" s="9"/>
       <c r="H356" s="9"/>
       <c r="I356" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J356" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K356" s="11"/>
@@ -9670,11 +9769,11 @@
       <c r="G357" s="9"/>
       <c r="H357" s="9"/>
       <c r="I357" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J357" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K357" s="11"/>
@@ -9692,11 +9791,11 @@
       <c r="G358" s="9"/>
       <c r="H358" s="9"/>
       <c r="I358" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J358" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K358" s="11"/>
@@ -9714,11 +9813,11 @@
       <c r="G359" s="9"/>
       <c r="H359" s="9"/>
       <c r="I359" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J359" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K359" s="11"/>
@@ -9736,11 +9835,11 @@
       <c r="G360" s="9"/>
       <c r="H360" s="9"/>
       <c r="I360" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J360" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K360" s="11"/>
@@ -9758,11 +9857,11 @@
       <c r="G361" s="9"/>
       <c r="H361" s="9"/>
       <c r="I361" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J361" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K361" s="11"/>
@@ -9780,11 +9879,11 @@
       <c r="G362" s="9"/>
       <c r="H362" s="9"/>
       <c r="I362" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J362" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K362" s="11"/>
@@ -9802,11 +9901,11 @@
       <c r="G363" s="9"/>
       <c r="H363" s="9"/>
       <c r="I363" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J363" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K363" s="11"/>
@@ -9824,11 +9923,11 @@
       <c r="G364" s="9"/>
       <c r="H364" s="9"/>
       <c r="I364" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J364" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K364" s="11"/>
@@ -9846,11 +9945,11 @@
       <c r="G365" s="9"/>
       <c r="H365" s="9"/>
       <c r="I365" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J365" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K365" s="11"/>
@@ -9868,11 +9967,11 @@
       <c r="G366" s="9"/>
       <c r="H366" s="9"/>
       <c r="I366" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J366" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K366" s="11"/>
@@ -9890,11 +9989,11 @@
       <c r="G367" s="9"/>
       <c r="H367" s="9"/>
       <c r="I367" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J367" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K367" s="11"/>
@@ -9912,11 +10011,11 @@
       <c r="G368" s="9"/>
       <c r="H368" s="9"/>
       <c r="I368" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J368" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K368" s="11"/>
@@ -9934,11 +10033,11 @@
       <c r="G369" s="9"/>
       <c r="H369" s="9"/>
       <c r="I369" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J369" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K369" s="11"/>
@@ -9956,11 +10055,11 @@
       <c r="G370" s="9"/>
       <c r="H370" s="9"/>
       <c r="I370" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J370" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K370" s="11"/>
@@ -9978,11 +10077,11 @@
       <c r="G371" s="9"/>
       <c r="H371" s="9"/>
       <c r="I371" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J371" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K371" s="11"/>
@@ -10000,11 +10099,11 @@
       <c r="G372" s="9"/>
       <c r="H372" s="9"/>
       <c r="I372" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J372" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K372" s="11"/>
@@ -10022,11 +10121,11 @@
       <c r="G373" s="9"/>
       <c r="H373" s="9"/>
       <c r="I373" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J373" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K373" s="11"/>
@@ -10044,11 +10143,11 @@
       <c r="G374" s="9"/>
       <c r="H374" s="9"/>
       <c r="I374" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J374" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K374" s="11"/>
@@ -10066,11 +10165,11 @@
       <c r="G375" s="9"/>
       <c r="H375" s="9"/>
       <c r="I375" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J375" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K375" s="11"/>
@@ -10088,11 +10187,11 @@
       <c r="G376" s="9"/>
       <c r="H376" s="9"/>
       <c r="I376" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J376" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K376" s="11"/>
@@ -10110,11 +10209,11 @@
       <c r="G377" s="9"/>
       <c r="H377" s="9"/>
       <c r="I377" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J377" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K377" s="11"/>
@@ -10132,11 +10231,11 @@
       <c r="G378" s="9"/>
       <c r="H378" s="9"/>
       <c r="I378" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J378" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K378" s="11"/>
@@ -10154,11 +10253,11 @@
       <c r="G379" s="9"/>
       <c r="H379" s="9"/>
       <c r="I379" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J379" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K379" s="11"/>
@@ -10176,11 +10275,11 @@
       <c r="G380" s="9"/>
       <c r="H380" s="9"/>
       <c r="I380" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J380" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K380" s="11"/>
@@ -10198,11 +10297,11 @@
       <c r="G381" s="9"/>
       <c r="H381" s="9"/>
       <c r="I381" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J381" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K381" s="11"/>
@@ -10220,11 +10319,11 @@
       <c r="G382" s="9"/>
       <c r="H382" s="9"/>
       <c r="I382" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J382" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K382" s="11"/>
@@ -10242,11 +10341,11 @@
       <c r="G383" s="9"/>
       <c r="H383" s="9"/>
       <c r="I383" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J383" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K383" s="11"/>
@@ -10264,11 +10363,11 @@
       <c r="G384" s="9"/>
       <c r="H384" s="9"/>
       <c r="I384" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J384" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K384" s="11"/>
@@ -10286,11 +10385,11 @@
       <c r="G385" s="9"/>
       <c r="H385" s="9"/>
       <c r="I385" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J385" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K385" s="11"/>
@@ -10308,11 +10407,11 @@
       <c r="G386" s="9"/>
       <c r="H386" s="9"/>
       <c r="I386" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J386" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K386" s="11"/>
@@ -10330,11 +10429,11 @@
       <c r="G387" s="9"/>
       <c r="H387" s="9"/>
       <c r="I387" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J387" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K387" s="11"/>
@@ -10352,11 +10451,11 @@
       <c r="G388" s="9"/>
       <c r="H388" s="9"/>
       <c r="I388" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J388" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K388" s="11"/>
@@ -10374,11 +10473,11 @@
       <c r="G389" s="9"/>
       <c r="H389" s="9"/>
       <c r="I389" s="10" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J389" s="10" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K389" s="11"/>
@@ -10396,11 +10495,11 @@
       <c r="G390" s="9"/>
       <c r="H390" s="9"/>
       <c r="I390" s="10" t="str">
-        <f t="shared" ref="I390:I401" si="15">IF(SUM(B389:F389,H390)=0,"",SUM(B389:F389,H390))</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J390" s="10" t="str">
-        <f t="shared" ref="J390:J401" si="16">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="K390" s="11"/>
@@ -10462,11 +10561,11 @@
       <c r="G393" s="9"/>
       <c r="H393" s="9"/>
       <c r="I393" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="I393:I404" si="17">IF(SUM(B392:F392,H393)=0,"",SUM(B392:F392,H393))</f>
         <v/>
       </c>
       <c r="J393" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="J393:J404" si="18">IF(I393="","",1440-I393)</f>
         <v/>
       </c>
       <c r="K393" s="11"/>
@@ -10484,11 +10583,11 @@
       <c r="G394" s="9"/>
       <c r="H394" s="9"/>
       <c r="I394" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J394" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K394" s="11"/>
@@ -10506,11 +10605,11 @@
       <c r="G395" s="9"/>
       <c r="H395" s="9"/>
       <c r="I395" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J395" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K395" s="11"/>
@@ -10528,11 +10627,11 @@
       <c r="G396" s="9"/>
       <c r="H396" s="9"/>
       <c r="I396" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J396" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K396" s="11"/>
@@ -10550,11 +10649,11 @@
       <c r="G397" s="9"/>
       <c r="H397" s="9"/>
       <c r="I397" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J397" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K397" s="11"/>
@@ -10572,11 +10671,11 @@
       <c r="G398" s="9"/>
       <c r="H398" s="9"/>
       <c r="I398" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J398" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K398" s="11"/>
@@ -10594,11 +10693,11 @@
       <c r="G399" s="9"/>
       <c r="H399" s="9"/>
       <c r="I399" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J399" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K399" s="11"/>
@@ -10616,11 +10715,11 @@
       <c r="G400" s="9"/>
       <c r="H400" s="9"/>
       <c r="I400" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J400" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K400" s="11"/>
@@ -10630,6 +10729,7 @@
     </row>
     <row r="401" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A401" s="8"/>
+      <c r="B401" s="9"/>
       <c r="C401" s="9"/>
       <c r="D401" s="9"/>
       <c r="E401" s="9"/>
@@ -10637,17 +10737,82 @@
       <c r="G401" s="9"/>
       <c r="H401" s="9"/>
       <c r="I401" s="10" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="J401" s="10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v/>
       </c>
       <c r="K401" s="11"/>
       <c r="L401" s="11"/>
       <c r="M401" s="11"/>
       <c r="N401" s="12"/>
+    </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A402" s="8"/>
+      <c r="B402" s="9"/>
+      <c r="C402" s="9"/>
+      <c r="D402" s="9"/>
+      <c r="E402" s="9"/>
+      <c r="F402" s="9"/>
+      <c r="G402" s="9"/>
+      <c r="H402" s="9"/>
+      <c r="I402" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="J402" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="K402" s="11"/>
+      <c r="L402" s="11"/>
+      <c r="M402" s="11"/>
+      <c r="N402" s="12"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A403" s="8"/>
+      <c r="B403" s="9"/>
+      <c r="C403" s="9"/>
+      <c r="D403" s="9"/>
+      <c r="E403" s="9"/>
+      <c r="F403" s="9"/>
+      <c r="G403" s="9"/>
+      <c r="H403" s="9"/>
+      <c r="I403" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="J403" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="K403" s="11"/>
+      <c r="L403" s="11"/>
+      <c r="M403" s="11"/>
+      <c r="N403" s="12"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A404" s="8"/>
+      <c r="C404" s="9"/>
+      <c r="D404" s="9"/>
+      <c r="E404" s="9"/>
+      <c r="F404" s="9"/>
+      <c r="G404" s="9"/>
+      <c r="H404" s="9"/>
+      <c r="I404" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="J404" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="K404" s="11"/>
+      <c r="L404" s="11"/>
+      <c r="M404" s="11"/>
+      <c r="N404" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10658,21 +10823,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J404">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K404" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L404" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M404" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E1E7A19-8908-4E12-AFB5-1EE3BA59D16F}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66E505D8-48CB-4206-BF55-D0DD0137D5F6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,12 @@
   </si>
   <si>
     <t>low</t>
+  </si>
+  <si>
+    <t>mumma is here today</t>
+  </si>
+  <si>
+    <t>travel back home</t>
   </si>
 </sst>
 </file>
@@ -2961,48 +2967,96 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B47" s="9">
+        <v>300</v>
+      </c>
+      <c r="C47" s="9">
+        <v>150</v>
+      </c>
+      <c r="D47" s="9">
+        <v>70</v>
+      </c>
+      <c r="E47" s="9">
+        <v>90</v>
+      </c>
+      <c r="F47" s="9">
+        <v>0</v>
+      </c>
+      <c r="G47" s="9">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9">
+        <v>300</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="12"/>
+        <v>530</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L47" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M47" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B48" s="9">
+        <v>480</v>
+      </c>
+      <c r="C48" s="9">
+        <v>160</v>
+      </c>
+      <c r="D48" s="9">
+        <v>80</v>
+      </c>
+      <c r="E48" s="9">
+        <v>80</v>
+      </c>
+      <c r="F48" s="9">
+        <v>0</v>
+      </c>
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
+        <v>190</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="11"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="12"/>
+        <v>450</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L48" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M48" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N48" s="12" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{66E505D8-48CB-4206-BF55-D0DD0137D5F6}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D100075C-3CCF-4E86-9BDC-0A91F7DFD7EE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>travel back home</t>
+  </si>
+  <si>
+    <t>day 1 of holiday at home</t>
   </si>
 </sst>
 </file>
@@ -955,8 +958,9 @@
   <dimension ref="A1:N404"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="6" width="11" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
@@ -3059,26 +3063,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B49" s="9">
+        <v>600</v>
+      </c>
+      <c r="C49" s="9">
+        <v>120</v>
+      </c>
+      <c r="D49" s="9">
+        <v>120</v>
+      </c>
+      <c r="E49" s="9">
+        <v>90</v>
+      </c>
+      <c r="F49" s="9">
+        <v>0</v>
+      </c>
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
+        <v>210</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="11"/>
-      <c r="M49" s="11"/>
-      <c r="N49" s="12"/>
+        <v>300</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L49" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M49" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N49" s="12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D100075C-3CCF-4E86-9BDC-0A91F7DFD7EE}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EDF1E68-206C-488F-8134-48C4D47A7F57}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -305,6 +305,9 @@
   </si>
   <si>
     <t>day 1 of holiday at home</t>
+  </si>
+  <si>
+    <t>day 2 of holiday at home</t>
   </si>
 </sst>
 </file>
@@ -960,7 +963,9 @@
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="6" width="11" customWidth="1"/>
+    <col min="3" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
@@ -3109,26 +3114,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B50" s="9">
+        <v>480</v>
+      </c>
+      <c r="C50" s="9">
+        <v>150</v>
+      </c>
+      <c r="D50" s="9">
+        <v>200</v>
+      </c>
+      <c r="E50" s="9">
+        <v>130</v>
+      </c>
+      <c r="F50" s="9">
+        <v>0</v>
+      </c>
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
+        <v>300</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="12"/>
+        <v>180</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L50" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M50" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="N50" s="12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EDF1E68-206C-488F-8134-48C4D47A7F57}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7D8772E-273C-4E7A-80E4-0A0FE09A415E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,9 +250,6 @@
     <t xml:space="preserve">An average day </t>
   </si>
   <si>
-    <t>September</t>
-  </si>
-  <si>
     <t>feeling  tired and stressed</t>
   </si>
   <si>
@@ -308,6 +305,12 @@
   </si>
   <si>
     <t>day 2 of holiday at home</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>day 3 of holiday at home</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1026,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1172,7 +1175,7 @@
         <v>56</v>
       </c>
       <c r="L7" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M7" s="16" t="s">
         <v>51</v>
@@ -1221,7 +1224,7 @@
         <v>57</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N8" s="17" t="s">
         <v>55</v>
@@ -1914,7 +1917,7 @@
         <v>51</v>
       </c>
       <c r="N23" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -1960,7 +1963,7 @@
         <v>61</v>
       </c>
       <c r="N24" s="12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -2000,13 +2003,13 @@
         <v>58</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M25" s="11" t="s">
         <v>58</v>
       </c>
       <c r="N25" s="12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2098,7 +2101,7 @@
         <v>51</v>
       </c>
       <c r="N27" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2236,7 +2239,7 @@
         <v>61</v>
       </c>
       <c r="N30" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2282,7 +2285,7 @@
         <v>51</v>
       </c>
       <c r="N31" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -2328,7 +2331,7 @@
         <v>61</v>
       </c>
       <c r="N32" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -2374,7 +2377,7 @@
         <v>51</v>
       </c>
       <c r="N33" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -2512,7 +2515,7 @@
         <v>51</v>
       </c>
       <c r="N36" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -2601,7 +2604,7 @@
         <v>60</v>
       </c>
       <c r="M38" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N38" s="12" t="s">
         <v>65</v>
@@ -2647,10 +2650,10 @@
         <v>60</v>
       </c>
       <c r="M39" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="N39" s="12" t="s">
         <v>84</v>
-      </c>
-      <c r="N39" s="12" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -2696,7 +2699,7 @@
         <v>58</v>
       </c>
       <c r="N40" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -2736,13 +2739,13 @@
         <v>49</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M41" s="11" t="s">
         <v>51</v>
       </c>
       <c r="N41" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -2828,7 +2831,7 @@
         <v>59</v>
       </c>
       <c r="L43" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M43" s="11" t="s">
         <v>51</v>
@@ -2880,7 +2883,7 @@
         <v>51</v>
       </c>
       <c r="N44" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -3018,7 +3021,7 @@
         <v>61</v>
       </c>
       <c r="N47" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -3064,7 +3067,7 @@
         <v>61</v>
       </c>
       <c r="N48" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -3110,7 +3113,7 @@
         <v>61</v>
       </c>
       <c r="N49" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -3153,33 +3156,57 @@
         <v>60</v>
       </c>
       <c r="M50" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N50" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="8"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B51" s="9">
+        <v>540</v>
+      </c>
+      <c r="C51" s="9">
+        <v>230</v>
+      </c>
+      <c r="D51" s="9">
+        <v>150</v>
+      </c>
+      <c r="E51" s="9">
+        <v>150</v>
+      </c>
+      <c r="F51" s="9">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
+        <v>300</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L51" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M51" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N51" s="12" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7D8772E-273C-4E7A-80E4-0A0FE09A415E}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93A845F2-C2D4-46F2-A05B-6D3EA882C52B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -311,6 +311,15 @@
   </si>
   <si>
     <t>day 3 of holiday at home</t>
+  </si>
+  <si>
+    <t>Trip to Khatu Shyam Ji</t>
+  </si>
+  <si>
+    <t>travel to salasar dham</t>
+  </si>
+  <si>
+    <t>day 1 of online classes</t>
   </si>
 </sst>
 </file>
@@ -3209,92 +3218,188 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="8"/>
-      <c r="B52" s="9"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="9"/>
-      <c r="H52" s="9"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B52" s="9">
+        <v>480</v>
+      </c>
+      <c r="C52" s="9">
+        <v>180</v>
+      </c>
+      <c r="D52" s="9">
+        <v>0</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0</v>
+      </c>
+      <c r="F52" s="9">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
+        <v>400</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="12"/>
+        <v>380</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L52" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M52" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N52" s="12" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="8"/>
-      <c r="B53" s="9"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B53" s="9">
+        <v>540</v>
+      </c>
+      <c r="C53" s="9">
+        <v>120</v>
+      </c>
+      <c r="D53" s="9">
+        <v>0</v>
+      </c>
+      <c r="E53" s="9">
+        <v>0</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0</v>
+      </c>
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
+        <v>450</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="12"/>
+        <v>330</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L53" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M53" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N53" s="12" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B54" s="9">
+        <v>230</v>
+      </c>
+      <c r="C54" s="9">
+        <v>250</v>
+      </c>
+      <c r="D54" s="9">
+        <v>100</v>
+      </c>
+      <c r="E54" s="9">
+        <v>0</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0</v>
+      </c>
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
+        <v>480</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="12"/>
+        <v>380</v>
+      </c>
+      <c r="K54" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L54" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M54" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="12" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="8"/>
-      <c r="B55" s="9"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B55" s="9">
+        <v>540</v>
+      </c>
+      <c r="C55" s="9">
+        <v>120</v>
+      </c>
+      <c r="D55" s="9">
+        <v>90</v>
+      </c>
+      <c r="E55" s="9">
+        <v>60</v>
+      </c>
+      <c r="F55" s="9">
+        <v>200</v>
+      </c>
+      <c r="G55" s="9">
+        <v>4</v>
+      </c>
+      <c r="H55" s="9">
+        <v>200</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
-      <c r="M55" s="11"/>
-      <c r="N55" s="12"/>
+        <v>230</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L55" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M55" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93A845F2-C2D4-46F2-A05B-6D3EA882C52B}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5887E27-1DA4-4C29-8E83-A133A4298D22}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -320,6 +320,12 @@
   </si>
   <si>
     <t>day 1 of online classes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market visiting </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wednesday fast </t>
   </si>
 </sst>
 </file>
@@ -3402,48 +3408,96 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="8"/>
-      <c r="B56" s="9"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="9">
+        <v>400</v>
+      </c>
+      <c r="C56" s="9">
+        <v>120</v>
+      </c>
+      <c r="D56" s="9">
+        <v>90</v>
+      </c>
+      <c r="E56" s="9">
+        <v>60</v>
+      </c>
+      <c r="F56" s="9">
+        <v>250</v>
+      </c>
+      <c r="G56" s="9">
+        <v>5</v>
+      </c>
+      <c r="H56" s="9">
+        <v>200</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="12"/>
+        <v>320</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L56" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N56" s="12" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="8"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="9">
+        <v>480</v>
+      </c>
+      <c r="C57" s="9">
+        <v>120</v>
+      </c>
+      <c r="D57" s="9">
+        <v>90</v>
+      </c>
+      <c r="E57" s="9">
+        <v>60</v>
+      </c>
+      <c r="F57" s="9">
+        <v>250</v>
+      </c>
+      <c r="G57" s="9">
+        <v>5</v>
+      </c>
+      <c r="H57" s="9">
+        <v>200</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="12"/>
+        <v>240</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L57" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="M57" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N57" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5887E27-1DA4-4C29-8E83-A133A4298D22}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D4CC85F-D474-4533-93EC-131742613253}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -464,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -490,20 +490,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -994,74 +985,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="17">
         <v>12624552</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1108,186 +1099,186 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="13">
+      <c r="A6" s="8">
         <v>46251</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="13">
         <v>370</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="14">
         <v>10</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="14">
         <v>30</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="9">
         <v>30</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="9">
         <v>300</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="9">
         <v>6</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="9">
         <v>60</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="14">
         <f>IF(SUM(B6:F6,H6)=0," ",SUM(B6:F6,H6))</f>
         <v>800</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="14">
         <f>IF(I6=" ","",1440-I6)</f>
         <v>640</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="16" t="s">
+      <c r="L6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="16" t="s">
+      <c r="M6" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="N6" s="17" t="s">
+      <c r="N6" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
+      <c r="A7" s="8">
         <v>46252</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>300</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="14">
         <v>20</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <v>80</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="9">
         <v>70</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="9">
         <v>350</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="9">
         <v>7</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="9">
         <v>70</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="14">
         <f t="shared" ref="I7:I12" si="0">IF(SUM(B7:F7,H7)=0," ",SUM(B7:F7,H7))</f>
         <v>890</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="14">
         <f t="shared" ref="J7:J13" si="1">IF(I7=" ","",1440-I7)</f>
         <v>550</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N7" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+      <c r="A8" s="8">
         <v>46253</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <v>350</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <v>50</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <v>80</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="9">
         <v>60</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="9">
         <v>350</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="9">
         <v>7</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="9">
         <v>90</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="14">
         <f t="shared" si="0"/>
         <v>980</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="14">
         <f t="shared" si="1"/>
         <v>460</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M8" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="N8" s="17" t="s">
+      <c r="N8" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
+      <c r="A9" s="8">
         <v>46254</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <v>270</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <v>50</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <v>60</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="9">
         <v>60</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="9">
         <v>200</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="9">
         <v>4</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="9">
         <v>80</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="14">
         <f t="shared" si="0"/>
         <v>720</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="14">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="L9" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M9" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N9" s="9" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1316,11 +1307,11 @@
       <c r="H10" s="9">
         <v>80</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="14">
         <f t="shared" si="0"/>
         <v>830</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J10" s="14">
         <f t="shared" si="1"/>
         <v>610</v>
       </c>
@@ -1362,11 +1353,11 @@
       <c r="H11" s="9">
         <v>50</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="14">
         <f t="shared" si="0"/>
         <v>520</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J11" s="14">
         <f t="shared" si="1"/>
         <v>920</v>
       </c>
@@ -1408,11 +1399,11 @@
       <c r="H12" s="9">
         <v>60</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="14">
         <f t="shared" si="0"/>
         <v>490</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="14">
         <f t="shared" si="1"/>
         <v>950</v>
       </c>
@@ -1454,11 +1445,11 @@
       <c r="H13" s="9">
         <v>30</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="14">
         <f t="shared" ref="I13:I44" si="2">IF(SUM(B13:F13,H13)=0," ",SUM(B13:F13,H13))</f>
         <v>610</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="14">
         <f t="shared" si="1"/>
         <v>830</v>
       </c>
@@ -1500,11 +1491,11 @@
       <c r="H14" s="9">
         <v>60</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="14">
         <f t="shared" si="2"/>
         <v>715</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="14">
         <f t="shared" ref="J14:J73" si="3">IF(I14=" ","",1440-I14)</f>
         <v>725</v>
       </c>
@@ -1546,11 +1537,11 @@
       <c r="H15" s="9">
         <v>70</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
         <f t="shared" si="2"/>
         <v>740</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="14">
         <f t="shared" si="3"/>
         <v>700</v>
       </c>
@@ -1592,11 +1583,11 @@
       <c r="H16" s="9">
         <v>40</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="14">
         <f t="shared" si="2"/>
         <v>810</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="14">
         <f t="shared" si="3"/>
         <v>630</v>
       </c>
@@ -1638,11 +1629,11 @@
       <c r="H17" s="9">
         <v>70</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="14">
         <f t="shared" si="2"/>
         <v>780</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="14">
         <f t="shared" si="3"/>
         <v>660</v>
       </c>
@@ -1684,11 +1675,11 @@
       <c r="H18" s="9">
         <v>70</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="14">
         <f t="shared" si="2"/>
         <v>660</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="14">
         <f t="shared" si="3"/>
         <v>780</v>
       </c>
@@ -1730,11 +1721,11 @@
       <c r="H19" s="9">
         <v>80</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="14">
         <f t="shared" si="2"/>
         <v>500</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="14">
         <f t="shared" si="3"/>
         <v>940</v>
       </c>
@@ -1776,11 +1767,11 @@
       <c r="H20" s="9">
         <v>90</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="14">
         <f t="shared" si="2"/>
         <v>690</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="14">
         <f t="shared" si="3"/>
         <v>750</v>
       </c>
@@ -1822,11 +1813,11 @@
       <c r="H21" s="9">
         <v>80</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="14">
         <f t="shared" si="2"/>
         <v>980</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="14">
         <f t="shared" si="3"/>
         <v>460</v>
       </c>
@@ -1868,11 +1859,11 @@
       <c r="H22" s="9">
         <v>70</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="14">
         <f t="shared" si="2"/>
         <v>770</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="14">
         <f t="shared" si="3"/>
         <v>670</v>
       </c>
@@ -1914,11 +1905,11 @@
       <c r="H23" s="9">
         <v>80</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="14">
         <f t="shared" si="2"/>
         <v>820</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="14">
         <f t="shared" si="3"/>
         <v>620</v>
       </c>
@@ -1960,11 +1951,11 @@
       <c r="H24" s="9">
         <v>90</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="14">
         <f t="shared" si="2"/>
         <v>1060</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="14">
         <f t="shared" si="3"/>
         <v>380</v>
       </c>
@@ -2006,11 +1997,11 @@
       <c r="H25" s="9">
         <v>80</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="14">
         <f t="shared" si="2"/>
         <v>660</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J25" s="14">
         <f t="shared" si="3"/>
         <v>780</v>
       </c>
@@ -2052,11 +2043,11 @@
       <c r="H26" s="9">
         <v>80</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="14">
         <f t="shared" si="2"/>
         <v>480</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="14">
         <f t="shared" si="3"/>
         <v>960</v>
       </c>
@@ -2098,11 +2089,11 @@
       <c r="H27" s="9">
         <v>90</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
         <f t="shared" si="2"/>
         <v>1200</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="14">
         <f t="shared" si="3"/>
         <v>240</v>
       </c>
@@ -2144,11 +2135,11 @@
       <c r="H28" s="9">
         <v>120</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="14">
         <f t="shared" si="2"/>
         <v>860</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="14">
         <f t="shared" si="3"/>
         <v>580</v>
       </c>
@@ -2190,11 +2181,11 @@
       <c r="H29" s="9">
         <v>130</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="14">
         <f t="shared" si="2"/>
         <v>990</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J29" s="14">
         <f t="shared" si="3"/>
         <v>450</v>
       </c>
@@ -2236,11 +2227,11 @@
       <c r="H30" s="9">
         <v>120</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="14">
         <f t="shared" si="2"/>
         <v>750</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J30" s="14">
         <f t="shared" si="3"/>
         <v>690</v>
       </c>
@@ -2282,11 +2273,11 @@
       <c r="H31" s="9">
         <v>120</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="14">
         <f t="shared" si="2"/>
         <v>1040</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J31" s="14">
         <f t="shared" si="3"/>
         <v>400</v>
       </c>
@@ -2328,11 +2319,11 @@
       <c r="H32" s="9">
         <v>300</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="14">
         <f t="shared" si="2"/>
         <v>800</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J32" s="14">
         <f t="shared" si="3"/>
         <v>640</v>
       </c>
@@ -2374,11 +2365,11 @@
       <c r="H33" s="9">
         <v>120</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="14">
         <f t="shared" si="2"/>
         <v>470</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J33" s="14">
         <f t="shared" si="3"/>
         <v>970</v>
       </c>
@@ -2420,11 +2411,11 @@
       <c r="H34" s="9">
         <v>120</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I34" s="14">
         <f t="shared" si="2"/>
         <v>810</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J34" s="14">
         <f t="shared" si="3"/>
         <v>630</v>
       </c>
@@ -2466,11 +2457,11 @@
       <c r="H35" s="9">
         <v>150</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I35" s="14">
         <f t="shared" si="2"/>
         <v>960</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J35" s="14">
         <f t="shared" si="3"/>
         <v>480</v>
       </c>
@@ -2512,11 +2503,11 @@
       <c r="H36" s="9">
         <v>150</v>
       </c>
-      <c r="I36" s="15">
+      <c r="I36" s="14">
         <f t="shared" si="2"/>
         <v>810</v>
       </c>
-      <c r="J36" s="15">
+      <c r="J36" s="14">
         <f t="shared" si="3"/>
         <v>630</v>
       </c>
@@ -2558,11 +2549,11 @@
       <c r="H37" s="9">
         <v>160</v>
       </c>
-      <c r="I37" s="15">
+      <c r="I37" s="14">
         <f t="shared" si="2"/>
         <v>1030</v>
       </c>
-      <c r="J37" s="15">
+      <c r="J37" s="14">
         <f t="shared" si="3"/>
         <v>410</v>
       </c>
@@ -2604,11 +2595,11 @@
       <c r="H38" s="9">
         <v>160</v>
       </c>
-      <c r="I38" s="15">
+      <c r="I38" s="14">
         <f t="shared" si="2"/>
         <v>1120</v>
       </c>
-      <c r="J38" s="15">
+      <c r="J38" s="14">
         <f t="shared" si="3"/>
         <v>320</v>
       </c>
@@ -2650,11 +2641,11 @@
       <c r="H39" s="9">
         <v>130</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <f t="shared" si="2"/>
         <v>780</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <f t="shared" si="3"/>
         <v>660</v>
       </c>
@@ -2696,11 +2687,11 @@
       <c r="H40" s="9">
         <v>180</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <f t="shared" si="2"/>
         <v>630</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <f t="shared" si="3"/>
         <v>810</v>
       </c>
@@ -2742,11 +2733,11 @@
       <c r="H41" s="9">
         <v>140</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <f t="shared" si="2"/>
         <v>880</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <f t="shared" si="3"/>
         <v>560</v>
       </c>
@@ -2788,11 +2779,11 @@
       <c r="H42" s="9">
         <v>120</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <f t="shared" si="2"/>
         <v>970</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <f t="shared" si="3"/>
         <v>470</v>
       </c>
@@ -2834,11 +2825,11 @@
       <c r="H43" s="9">
         <v>150</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <f t="shared" si="2"/>
         <v>900</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <f t="shared" si="3"/>
         <v>540</v>
       </c>
@@ -2880,11 +2871,11 @@
       <c r="H44" s="9">
         <v>180</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <f t="shared" si="2"/>
         <v>1130</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <f t="shared" si="3"/>
         <v>310</v>
       </c>
@@ -2926,11 +2917,11 @@
       <c r="H45" s="9">
         <v>180</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <f t="shared" ref="I45:I73" si="4">IF(SUM(B45:F45,H45)=0," ",SUM(B45:F45,H45))</f>
         <v>1000</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <f t="shared" si="3"/>
         <v>440</v>
       </c>
@@ -2972,11 +2963,11 @@
       <c r="H46" s="9">
         <v>190</v>
       </c>
-      <c r="I46" s="15">
+      <c r="I46" s="14">
         <f t="shared" si="4"/>
         <v>720</v>
       </c>
-      <c r="J46" s="15">
+      <c r="J46" s="14">
         <f t="shared" si="3"/>
         <v>720</v>
       </c>
@@ -3018,11 +3009,11 @@
       <c r="H47" s="9">
         <v>300</v>
       </c>
-      <c r="I47" s="15">
+      <c r="I47" s="14">
         <f t="shared" si="4"/>
         <v>910</v>
       </c>
-      <c r="J47" s="15">
+      <c r="J47" s="14">
         <f t="shared" si="3"/>
         <v>530</v>
       </c>
@@ -3064,11 +3055,11 @@
       <c r="H48" s="9">
         <v>190</v>
       </c>
-      <c r="I48" s="15">
+      <c r="I48" s="14">
         <f t="shared" si="4"/>
         <v>990</v>
       </c>
-      <c r="J48" s="15">
+      <c r="J48" s="14">
         <f t="shared" si="3"/>
         <v>450</v>
       </c>
@@ -3110,11 +3101,11 @@
       <c r="H49" s="9">
         <v>210</v>
       </c>
-      <c r="I49" s="15">
+      <c r="I49" s="14">
         <f t="shared" si="4"/>
         <v>1140</v>
       </c>
-      <c r="J49" s="15">
+      <c r="J49" s="14">
         <f t="shared" si="3"/>
         <v>300</v>
       </c>
@@ -3156,11 +3147,11 @@
       <c r="H50" s="9">
         <v>300</v>
       </c>
-      <c r="I50" s="15">
+      <c r="I50" s="14">
         <f t="shared" si="4"/>
         <v>1260</v>
       </c>
-      <c r="J50" s="15">
+      <c r="J50" s="14">
         <f t="shared" si="3"/>
         <v>180</v>
       </c>
@@ -3202,11 +3193,11 @@
       <c r="H51" s="9">
         <v>300</v>
       </c>
-      <c r="I51" s="15">
+      <c r="I51" s="14">
         <f t="shared" si="4"/>
         <v>1370</v>
       </c>
-      <c r="J51" s="15">
+      <c r="J51" s="14">
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
@@ -3248,11 +3239,11 @@
       <c r="H52" s="9">
         <v>400</v>
       </c>
-      <c r="I52" s="15">
+      <c r="I52" s="14">
         <f t="shared" si="4"/>
         <v>1060</v>
       </c>
-      <c r="J52" s="15">
+      <c r="J52" s="14">
         <f t="shared" si="3"/>
         <v>380</v>
       </c>
@@ -3294,11 +3285,11 @@
       <c r="H53" s="9">
         <v>450</v>
       </c>
-      <c r="I53" s="15">
+      <c r="I53" s="14">
         <f t="shared" si="4"/>
         <v>1110</v>
       </c>
-      <c r="J53" s="15">
+      <c r="J53" s="14">
         <f t="shared" si="3"/>
         <v>330</v>
       </c>
@@ -3340,11 +3331,11 @@
       <c r="H54" s="9">
         <v>480</v>
       </c>
-      <c r="I54" s="15">
+      <c r="I54" s="14">
         <f t="shared" si="4"/>
         <v>1060</v>
       </c>
-      <c r="J54" s="15">
+      <c r="J54" s="14">
         <f t="shared" si="3"/>
         <v>380</v>
       </c>
@@ -3386,11 +3377,11 @@
       <c r="H55" s="9">
         <v>200</v>
       </c>
-      <c r="I55" s="15">
+      <c r="I55" s="14">
         <f t="shared" si="4"/>
         <v>1210</v>
       </c>
-      <c r="J55" s="15">
+      <c r="J55" s="14">
         <f t="shared" si="3"/>
         <v>230</v>
       </c>
@@ -3432,11 +3423,11 @@
       <c r="H56" s="9">
         <v>200</v>
       </c>
-      <c r="I56" s="15">
+      <c r="I56" s="14">
         <f t="shared" si="4"/>
         <v>1120</v>
       </c>
-      <c r="J56" s="15">
+      <c r="J56" s="14">
         <f t="shared" si="3"/>
         <v>320</v>
       </c>
@@ -3478,11 +3469,11 @@
       <c r="H57" s="9">
         <v>200</v>
       </c>
-      <c r="I57" s="15">
+      <c r="I57" s="14">
         <f t="shared" si="4"/>
         <v>1200</v>
       </c>
-      <c r="J57" s="15">
+      <c r="J57" s="14">
         <f t="shared" si="3"/>
         <v>240</v>
       </c>
@@ -3500,26 +3491,50 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="8"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="9">
+        <v>480</v>
+      </c>
+      <c r="C58" s="9">
+        <v>120</v>
+      </c>
+      <c r="D58" s="9">
+        <v>150</v>
+      </c>
+      <c r="E58" s="9">
+        <v>120</v>
+      </c>
+      <c r="F58" s="9">
+        <v>120</v>
+      </c>
+      <c r="G58" s="9">
+        <v>2</v>
+      </c>
+      <c r="H58" s="9">
+        <v>150</v>
+      </c>
+      <c r="I58" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J58" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K58" s="11"/>
-      <c r="L58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="12"/>
+        <v>300</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M58" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="8"/>
@@ -3530,11 +3545,11 @@
       <c r="F59" s="9"/>
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
-      <c r="I59" s="15" t="str">
+      <c r="I59" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J59" s="15" t="str">
+      <c r="J59" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3552,11 +3567,11 @@
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
-      <c r="I60" s="15" t="str">
+      <c r="I60" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J60" s="15" t="str">
+      <c r="J60" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3574,11 +3589,11 @@
       <c r="F61" s="9"/>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
-      <c r="I61" s="15" t="str">
+      <c r="I61" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J61" s="15" t="str">
+      <c r="J61" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3596,11 +3611,11 @@
       <c r="F62" s="9"/>
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
-      <c r="I62" s="15" t="str">
+      <c r="I62" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J62" s="15" t="str">
+      <c r="J62" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3618,11 +3633,11 @@
       <c r="F63" s="9"/>
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
-      <c r="I63" s="15" t="str">
+      <c r="I63" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J63" s="15" t="str">
+      <c r="J63" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3640,11 +3655,11 @@
       <c r="F64" s="9"/>
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
-      <c r="I64" s="15" t="str">
+      <c r="I64" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J64" s="15" t="str">
+      <c r="J64" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3662,11 +3677,11 @@
       <c r="F65" s="9"/>
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
-      <c r="I65" s="15" t="str">
+      <c r="I65" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J65" s="15" t="str">
+      <c r="J65" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3684,11 +3699,11 @@
       <c r="F66" s="9"/>
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
-      <c r="I66" s="15" t="str">
+      <c r="I66" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J66" s="15" t="str">
+      <c r="J66" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3706,11 +3721,11 @@
       <c r="F67" s="9"/>
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
-      <c r="I67" s="15" t="str">
+      <c r="I67" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J67" s="15" t="str">
+      <c r="J67" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3728,11 +3743,11 @@
       <c r="F68" s="9"/>
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
-      <c r="I68" s="15" t="str">
+      <c r="I68" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J68" s="15" t="str">
+      <c r="J68" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3750,11 +3765,11 @@
       <c r="F69" s="9"/>
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
-      <c r="I69" s="15" t="str">
+      <c r="I69" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J69" s="15" t="str">
+      <c r="J69" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3772,11 +3787,11 @@
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
-      <c r="I70" s="15" t="str">
+      <c r="I70" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J70" s="15" t="str">
+      <c r="J70" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3794,11 +3809,11 @@
       <c r="F71" s="9"/>
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
-      <c r="I71" s="15" t="str">
+      <c r="I71" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J71" s="15" t="str">
+      <c r="J71" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3816,11 +3831,11 @@
       <c r="F72" s="9"/>
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
-      <c r="I72" s="15" t="str">
+      <c r="I72" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J72" s="15" t="str">
+      <c r="J72" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3838,11 +3853,11 @@
       <c r="F73" s="9"/>
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
-      <c r="I73" s="15" t="str">
+      <c r="I73" s="14" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J73" s="15" t="str">
+      <c r="J73" s="14" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -3860,11 +3875,11 @@
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
-      <c r="I74" s="15" t="str">
+      <c r="I74" s="14" t="str">
         <f t="shared" ref="I74:I117" si="5">IF(SUM(B74:F74,H74)=0," ",SUM(B74:F74,H74))</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J74" s="15" t="str">
+      <c r="J74" s="14" t="str">
         <f t="shared" ref="J74:J117" si="6">IF(I74=" ","",1440-I74)</f>
         <v/>
       </c>
@@ -3882,11 +3897,11 @@
       <c r="F75" s="9"/>
       <c r="G75" s="9"/>
       <c r="H75" s="9"/>
-      <c r="I75" s="15" t="str">
+      <c r="I75" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J75" s="15" t="str">
+      <c r="J75" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -3904,11 +3919,11 @@
       <c r="F76" s="9"/>
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
-      <c r="I76" s="15" t="str">
+      <c r="I76" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J76" s="15" t="str">
+      <c r="J76" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -3926,11 +3941,11 @@
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
-      <c r="I77" s="15" t="str">
+      <c r="I77" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J77" s="15" t="str">
+      <c r="J77" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -3948,11 +3963,11 @@
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
-      <c r="I78" s="15" t="str">
+      <c r="I78" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J78" s="15" t="str">
+      <c r="J78" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -3970,11 +3985,11 @@
       <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
-      <c r="I79" s="15" t="str">
+      <c r="I79" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J79" s="15" t="str">
+      <c r="J79" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -3992,11 +4007,11 @@
       <c r="F80" s="9"/>
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
-      <c r="I80" s="15" t="str">
+      <c r="I80" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J80" s="15" t="str">
+      <c r="J80" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4014,11 +4029,11 @@
       <c r="F81" s="9"/>
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
-      <c r="I81" s="15" t="str">
+      <c r="I81" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J81" s="15" t="str">
+      <c r="J81" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4036,11 +4051,11 @@
       <c r="F82" s="9"/>
       <c r="G82" s="9"/>
       <c r="H82" s="9"/>
-      <c r="I82" s="15" t="str">
+      <c r="I82" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J82" s="15" t="str">
+      <c r="J82" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4058,11 +4073,11 @@
       <c r="F83" s="9"/>
       <c r="G83" s="9"/>
       <c r="H83" s="9"/>
-      <c r="I83" s="15" t="str">
+      <c r="I83" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J83" s="15" t="str">
+      <c r="J83" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4080,11 +4095,11 @@
       <c r="F84" s="9"/>
       <c r="G84" s="9"/>
       <c r="H84" s="9"/>
-      <c r="I84" s="15" t="str">
+      <c r="I84" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J84" s="15" t="str">
+      <c r="J84" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4102,11 +4117,11 @@
       <c r="F85" s="9"/>
       <c r="G85" s="9"/>
       <c r="H85" s="9"/>
-      <c r="I85" s="15" t="str">
+      <c r="I85" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J85" s="15" t="str">
+      <c r="J85" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4124,11 +4139,11 @@
       <c r="F86" s="9"/>
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
-      <c r="I86" s="15" t="str">
+      <c r="I86" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J86" s="15" t="str">
+      <c r="J86" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4146,11 +4161,11 @@
       <c r="F87" s="9"/>
       <c r="G87" s="9"/>
       <c r="H87" s="9"/>
-      <c r="I87" s="15" t="str">
+      <c r="I87" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J87" s="15" t="str">
+      <c r="J87" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4168,11 +4183,11 @@
       <c r="F88" s="9"/>
       <c r="G88" s="9"/>
       <c r="H88" s="9"/>
-      <c r="I88" s="15" t="str">
+      <c r="I88" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J88" s="15" t="str">
+      <c r="J88" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4190,11 +4205,11 @@
       <c r="F89" s="9"/>
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
-      <c r="I89" s="15" t="str">
+      <c r="I89" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J89" s="15" t="str">
+      <c r="J89" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4212,11 +4227,11 @@
       <c r="F90" s="9"/>
       <c r="G90" s="9"/>
       <c r="H90" s="9"/>
-      <c r="I90" s="15" t="str">
+      <c r="I90" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J90" s="15" t="str">
+      <c r="J90" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4234,11 +4249,11 @@
       <c r="F91" s="9"/>
       <c r="G91" s="9"/>
       <c r="H91" s="9"/>
-      <c r="I91" s="15" t="str">
+      <c r="I91" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J91" s="15" t="str">
+      <c r="J91" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4256,11 +4271,11 @@
       <c r="F92" s="9"/>
       <c r="G92" s="9"/>
       <c r="H92" s="9"/>
-      <c r="I92" s="15" t="str">
+      <c r="I92" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J92" s="15" t="str">
+      <c r="J92" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4278,11 +4293,11 @@
       <c r="F93" s="9"/>
       <c r="G93" s="9"/>
       <c r="H93" s="9"/>
-      <c r="I93" s="15" t="str">
+      <c r="I93" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J93" s="15" t="str">
+      <c r="J93" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4300,11 +4315,11 @@
       <c r="F94" s="9"/>
       <c r="G94" s="9"/>
       <c r="H94" s="9"/>
-      <c r="I94" s="15" t="str">
+      <c r="I94" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J94" s="15" t="str">
+      <c r="J94" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4322,11 +4337,11 @@
       <c r="F95" s="9"/>
       <c r="G95" s="9"/>
       <c r="H95" s="9"/>
-      <c r="I95" s="15" t="str">
+      <c r="I95" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J95" s="15" t="str">
+      <c r="J95" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4344,11 +4359,11 @@
       <c r="F96" s="9"/>
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
-      <c r="I96" s="15" t="str">
+      <c r="I96" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J96" s="15" t="str">
+      <c r="J96" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4366,11 +4381,11 @@
       <c r="F97" s="9"/>
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
-      <c r="I97" s="15" t="str">
+      <c r="I97" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J97" s="15" t="str">
+      <c r="J97" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4388,11 +4403,11 @@
       <c r="F98" s="9"/>
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
-      <c r="I98" s="15" t="str">
+      <c r="I98" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J98" s="15" t="str">
+      <c r="J98" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4410,11 +4425,11 @@
       <c r="F99" s="9"/>
       <c r="G99" s="9"/>
       <c r="H99" s="9"/>
-      <c r="I99" s="15" t="str">
+      <c r="I99" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J99" s="15" t="str">
+      <c r="J99" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4432,11 +4447,11 @@
       <c r="F100" s="9"/>
       <c r="G100" s="9"/>
       <c r="H100" s="9"/>
-      <c r="I100" s="15" t="str">
+      <c r="I100" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J100" s="15" t="str">
+      <c r="J100" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4454,11 +4469,11 @@
       <c r="F101" s="9"/>
       <c r="G101" s="9"/>
       <c r="H101" s="9"/>
-      <c r="I101" s="15" t="str">
+      <c r="I101" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J101" s="15" t="str">
+      <c r="J101" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4476,11 +4491,11 @@
       <c r="F102" s="9"/>
       <c r="G102" s="9"/>
       <c r="H102" s="9"/>
-      <c r="I102" s="15" t="str">
+      <c r="I102" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J102" s="15" t="str">
+      <c r="J102" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4498,11 +4513,11 @@
       <c r="F103" s="9"/>
       <c r="G103" s="9"/>
       <c r="H103" s="9"/>
-      <c r="I103" s="15" t="str">
+      <c r="I103" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J103" s="15" t="str">
+      <c r="J103" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4520,11 +4535,11 @@
       <c r="F104" s="9"/>
       <c r="G104" s="9"/>
       <c r="H104" s="9"/>
-      <c r="I104" s="15" t="str">
+      <c r="I104" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J104" s="15" t="str">
+      <c r="J104" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4542,11 +4557,11 @@
       <c r="F105" s="9"/>
       <c r="G105" s="9"/>
       <c r="H105" s="9"/>
-      <c r="I105" s="15" t="str">
+      <c r="I105" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J105" s="15" t="str">
+      <c r="J105" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4564,11 +4579,11 @@
       <c r="F106" s="9"/>
       <c r="G106" s="9"/>
       <c r="H106" s="9"/>
-      <c r="I106" s="15" t="str">
+      <c r="I106" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J106" s="15" t="str">
+      <c r="J106" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4586,11 +4601,11 @@
       <c r="F107" s="9"/>
       <c r="G107" s="9"/>
       <c r="H107" s="9"/>
-      <c r="I107" s="15" t="str">
+      <c r="I107" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J107" s="15" t="str">
+      <c r="J107" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4608,11 +4623,11 @@
       <c r="F108" s="9"/>
       <c r="G108" s="9"/>
       <c r="H108" s="9"/>
-      <c r="I108" s="15" t="str">
+      <c r="I108" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J108" s="15" t="str">
+      <c r="J108" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4630,11 +4645,11 @@
       <c r="F109" s="9"/>
       <c r="G109" s="9"/>
       <c r="H109" s="9"/>
-      <c r="I109" s="15" t="str">
+      <c r="I109" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J109" s="15" t="str">
+      <c r="J109" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4652,11 +4667,11 @@
       <c r="F110" s="9"/>
       <c r="G110" s="9"/>
       <c r="H110" s="9"/>
-      <c r="I110" s="15" t="str">
+      <c r="I110" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J110" s="15" t="str">
+      <c r="J110" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4674,11 +4689,11 @@
       <c r="F111" s="9"/>
       <c r="G111" s="9"/>
       <c r="H111" s="9"/>
-      <c r="I111" s="15" t="str">
+      <c r="I111" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J111" s="15" t="str">
+      <c r="J111" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4696,11 +4711,11 @@
       <c r="F112" s="9"/>
       <c r="G112" s="9"/>
       <c r="H112" s="9"/>
-      <c r="I112" s="15" t="str">
+      <c r="I112" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J112" s="15" t="str">
+      <c r="J112" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4718,11 +4733,11 @@
       <c r="F113" s="9"/>
       <c r="G113" s="9"/>
       <c r="H113" s="9"/>
-      <c r="I113" s="15" t="str">
+      <c r="I113" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J113" s="15" t="str">
+      <c r="J113" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4740,11 +4755,11 @@
       <c r="F114" s="9"/>
       <c r="G114" s="9"/>
       <c r="H114" s="9"/>
-      <c r="I114" s="15" t="str">
+      <c r="I114" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J114" s="15" t="str">
+      <c r="J114" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4762,11 +4777,11 @@
       <c r="F115" s="9"/>
       <c r="G115" s="9"/>
       <c r="H115" s="9"/>
-      <c r="I115" s="15" t="str">
+      <c r="I115" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J115" s="15" t="str">
+      <c r="J115" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4784,11 +4799,11 @@
       <c r="F116" s="9"/>
       <c r="G116" s="9"/>
       <c r="H116" s="9"/>
-      <c r="I116" s="15" t="str">
+      <c r="I116" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J116" s="15" t="str">
+      <c r="J116" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4806,11 +4821,11 @@
       <c r="F117" s="9"/>
       <c r="G117" s="9"/>
       <c r="H117" s="9"/>
-      <c r="I117" s="15" t="str">
+      <c r="I117" s="14" t="str">
         <f t="shared" si="5"/>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="J117" s="15" t="str">
+      <c r="J117" s="14" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -4832,7 +4847,7 @@
         <f t="shared" ref="I118:I136" si="7">IF(SUM(B117:F117,H118)=0,"",SUM(B117:F117,H118))</f>
         <v/>
       </c>
-      <c r="J118" s="15"/>
+      <c r="J118" s="14"/>
       <c r="K118" s="11"/>
       <c r="L118" s="11"/>
       <c r="M118" s="11"/>
@@ -4851,7 +4866,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J119" s="15"/>
+      <c r="J119" s="14"/>
       <c r="K119" s="11"/>
       <c r="L119" s="11"/>
       <c r="M119" s="11"/>
@@ -4870,7 +4885,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J120" s="15"/>
+      <c r="J120" s="14"/>
       <c r="K120" s="11"/>
       <c r="L120" s="11"/>
       <c r="M120" s="11"/>
@@ -4889,7 +4904,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J121" s="15"/>
+      <c r="J121" s="14"/>
       <c r="K121" s="11"/>
       <c r="L121" s="11"/>
       <c r="M121" s="11"/>
@@ -4908,7 +4923,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J122" s="15"/>
+      <c r="J122" s="14"/>
       <c r="K122" s="11"/>
       <c r="L122" s="11"/>
       <c r="M122" s="11"/>
@@ -4927,7 +4942,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J123" s="15"/>
+      <c r="J123" s="14"/>
       <c r="K123" s="11"/>
       <c r="L123" s="11"/>
       <c r="M123" s="11"/>
@@ -4946,7 +4961,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="J124" s="15"/>
+      <c r="J124" s="14"/>
       <c r="K124" s="11"/>
       <c r="L124" s="11"/>
       <c r="M124" s="11"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D4CC85F-D474-4533-93EC-131742613253}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69106E3C-B8DF-443B-9D4B-569B4A3A4C34}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t xml:space="preserve">Wednesday fast </t>
+  </si>
+  <si>
+    <t>day full of thoughts</t>
   </si>
 </sst>
 </file>
@@ -3537,26 +3540,50 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="8"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="14" t="str">
+      <c r="A59" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="9">
+        <v>300</v>
+      </c>
+      <c r="C59" s="9">
+        <v>150</v>
+      </c>
+      <c r="D59" s="9">
+        <v>200</v>
+      </c>
+      <c r="E59" s="9">
+        <v>100</v>
+      </c>
+      <c r="F59" s="9">
+        <v>0</v>
+      </c>
+      <c r="G59" s="9">
+        <v>0</v>
+      </c>
+      <c r="H59" s="9">
+        <v>300</v>
+      </c>
+      <c r="I59" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J59" s="14" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J59" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K59" s="11"/>
-      <c r="L59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="12"/>
+        <v>390</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N59" s="12" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69106E3C-B8DF-443B-9D4B-569B4A3A4C34}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55C3B195-C436-4D60-B5F8-C5BE94A98C73}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t>day full of thoughts</t>
+  </si>
+  <si>
+    <t>feeling low &amp; come back to lpu</t>
   </si>
 </sst>
 </file>
@@ -3585,27 +3588,51 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="8"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
-      <c r="I60" s="14" t="str">
+    <row r="60" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B60" s="9">
+        <v>660</v>
+      </c>
+      <c r="C60" s="9">
+        <v>300</v>
+      </c>
+      <c r="D60" s="9">
+        <v>0</v>
+      </c>
+      <c r="E60" s="9">
+        <v>0</v>
+      </c>
+      <c r="F60" s="9">
+        <v>0</v>
+      </c>
+      <c r="G60" s="9">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9">
+        <v>250</v>
+      </c>
+      <c r="I60" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J60" s="14" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J60" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K60" s="11"/>
-      <c r="L60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="12"/>
+        <v>230</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="12" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55C3B195-C436-4D60-B5F8-C5BE94A98C73}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFE56C58-CE68-4883-997C-33116E9D37E1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3635,26 +3635,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="8"/>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="14" t="str">
+      <c r="A61" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="9">
+        <v>480</v>
+      </c>
+      <c r="C61" s="9">
+        <v>120</v>
+      </c>
+      <c r="D61" s="9">
+        <v>500</v>
+      </c>
+      <c r="E61" s="9">
+        <v>100</v>
+      </c>
+      <c r="F61" s="9">
+        <v>0</v>
+      </c>
+      <c r="G61" s="9">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9">
+        <v>200</v>
+      </c>
+      <c r="I61" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J61" s="14" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J61" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N61" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFE56C58-CE68-4883-997C-33116E9D37E1}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FF9A18F-CD4B-4072-A0DF-B14CC9102B24}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>feeling low &amp; come back to lpu</t>
+  </si>
+  <si>
+    <t>mid term exam of CAP-7001</t>
   </si>
 </sst>
 </file>
@@ -3681,26 +3684,50 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="8"/>
-      <c r="B62" s="9"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="14" t="str">
+      <c r="A62" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="9">
+        <v>240</v>
+      </c>
+      <c r="C62" s="9">
+        <v>150</v>
+      </c>
+      <c r="D62" s="9">
+        <v>500</v>
+      </c>
+      <c r="E62" s="9">
+        <v>0</v>
+      </c>
+      <c r="F62" s="9">
+        <v>0</v>
+      </c>
+      <c r="G62" s="9">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9">
+        <v>300</v>
+      </c>
+      <c r="I62" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J62" s="14" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J62" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="12"/>
+        <v>250</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="12" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FF9A18F-CD4B-4072-A0DF-B14CC9102B24}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBEC0A56-AC8C-4328-A35A-C7D908485779}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3730,26 +3730,50 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="8"/>
-      <c r="B63" s="9"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="14" t="str">
+      <c r="A63" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="9">
+        <v>400</v>
+      </c>
+      <c r="C63" s="9">
+        <v>150</v>
+      </c>
+      <c r="D63" s="9">
+        <v>480</v>
+      </c>
+      <c r="E63" s="9">
+        <v>0</v>
+      </c>
+      <c r="F63" s="9">
+        <v>0</v>
+      </c>
+      <c r="G63" s="9">
+        <v>0</v>
+      </c>
+      <c r="H63" s="9">
+        <v>300</v>
+      </c>
+      <c r="I63" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J63" s="14" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J63" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="12"/>
+        <v>110</v>
+      </c>
+      <c r="K63" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L63" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N63" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBEC0A56-AC8C-4328-A35A-C7D908485779}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C12434B-F037-42AA-902F-F7DA0B700B6C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>mid term exam of CAP-7001</t>
+  </si>
+  <si>
+    <t>MTT of DBMS &amp; Wed. fast</t>
   </si>
 </sst>
 </file>
@@ -3776,26 +3779,50 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="8"/>
-      <c r="B64" s="9"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="14" t="str">
+      <c r="A64" s="8">
+        <v>46309</v>
+      </c>
+      <c r="B64" s="9">
+        <v>450</v>
+      </c>
+      <c r="C64" s="9">
+        <v>140</v>
+      </c>
+      <c r="D64" s="9">
+        <v>560</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0</v>
+      </c>
+      <c r="F64" s="9">
+        <v>0</v>
+      </c>
+      <c r="G64" s="9">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
+        <v>250</v>
+      </c>
+      <c r="I64" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J64" s="14" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J64" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K64" s="11"/>
-      <c r="L64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L64" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M64" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N64" s="12" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C12434B-F037-42AA-902F-F7DA0B700B6C}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0343EF46-7716-41E4-8C27-69CB7823EB96}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3825,26 +3825,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="8"/>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="14" t="str">
+      <c r="A65" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="9">
+        <v>420</v>
+      </c>
+      <c r="C65" s="9">
+        <v>140</v>
+      </c>
+      <c r="D65" s="9">
+        <v>500</v>
+      </c>
+      <c r="E65" s="9">
+        <v>200</v>
+      </c>
+      <c r="F65" s="9">
+        <v>0</v>
+      </c>
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
+        <v>150</v>
+      </c>
+      <c r="I65" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J65" s="14" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J65" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K65" s="11"/>
-      <c r="L65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="12"/>
+        <v>30</v>
+      </c>
+      <c r="K65" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N65" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0343EF46-7716-41E4-8C27-69CB7823EB96}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFE6326D-E99F-4B58-A7D7-6BEB99EFD599}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t>MTT of DBMS &amp; Wed. fast</t>
+  </si>
+  <si>
+    <t>MTT of PEA-515</t>
   </si>
 </sst>
 </file>
@@ -3871,26 +3874,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="8"/>
-      <c r="B66" s="9"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="14" t="str">
+      <c r="A66" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="9">
+        <v>360</v>
+      </c>
+      <c r="C66" s="9">
+        <v>150</v>
+      </c>
+      <c r="D66" s="9">
+        <v>500</v>
+      </c>
+      <c r="E66" s="9">
+        <v>300</v>
+      </c>
+      <c r="F66" s="9">
+        <v>0</v>
+      </c>
+      <c r="G66" s="9">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
+        <v>100</v>
+      </c>
+      <c r="I66" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J66" s="14" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J66" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="12"/>
+        <v>30</v>
+      </c>
+      <c r="K66" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L66" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="12" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFE6326D-E99F-4B58-A7D7-6BEB99EFD599}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{249E1ACB-D08D-4297-B039-85AA0F7F29D0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,9 @@
   </si>
   <si>
     <t>MTT of PEA-515</t>
+  </si>
+  <si>
+    <t>MTT of PEL-546</t>
   </si>
 </sst>
 </file>
@@ -3920,26 +3923,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="8"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="14" t="str">
+      <c r="A67" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="9">
+        <v>540</v>
+      </c>
+      <c r="C67" s="9">
+        <v>140</v>
+      </c>
+      <c r="D67" s="9">
+        <v>320</v>
+      </c>
+      <c r="E67" s="9">
+        <v>300</v>
+      </c>
+      <c r="F67" s="9">
+        <v>0</v>
+      </c>
+      <c r="G67" s="9">
+        <v>0</v>
+      </c>
+      <c r="H67" s="9">
+        <v>100</v>
+      </c>
+      <c r="I67" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J67" s="14" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J67" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K67" s="11"/>
-      <c r="L67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="K67" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L67" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M67" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N67" s="12" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{249E1ACB-D08D-4297-B039-85AA0F7F29D0}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A45468-6871-4696-8890-FD29DA429FFD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3969,26 +3969,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="8"/>
-      <c r="B68" s="9"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="14" t="str">
+      <c r="A68" s="8">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="9">
+        <v>300</v>
+      </c>
+      <c r="C68" s="9">
+        <v>150</v>
+      </c>
+      <c r="D68" s="9">
+        <v>400</v>
+      </c>
+      <c r="E68" s="9">
+        <v>400</v>
+      </c>
+      <c r="F68" s="9">
+        <v>0</v>
+      </c>
+      <c r="G68" s="9">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
+        <v>150</v>
+      </c>
+      <c r="I68" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J68" s="14" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J68" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K68" s="11"/>
-      <c r="L68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="K68" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L68" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M68" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N68" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A45468-6871-4696-8890-FD29DA429FFD}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC1568EE-0AD4-48C3-B6D7-5A56FC3D2096}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t>MTT of PEL-546</t>
+  </si>
+  <si>
+    <t>first day after holidays</t>
   </si>
 </sst>
 </file>
@@ -4015,26 +4018,50 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="8"/>
-      <c r="B69" s="9"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="14" t="str">
+      <c r="A69" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="9">
+        <v>450</v>
+      </c>
+      <c r="C69" s="9">
+        <v>140</v>
+      </c>
+      <c r="D69" s="9">
+        <v>300</v>
+      </c>
+      <c r="E69" s="9">
+        <v>200</v>
+      </c>
+      <c r="F69" s="9">
+        <v>200</v>
+      </c>
+      <c r="G69" s="9">
+        <v>4</v>
+      </c>
+      <c r="H69" s="9">
+        <v>150</v>
+      </c>
+      <c r="I69" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J69" s="14" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J69" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K69" s="11"/>
-      <c r="L69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="K69" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L69" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M69" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N69" s="12" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC1568EE-0AD4-48C3-B6D7-5A56FC3D2096}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4C111E1-4C25-45F8-B604-CC042A95D521}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>first day after holidays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dussehra holiday </t>
   </si>
 </sst>
 </file>
@@ -4064,26 +4067,50 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="8"/>
-      <c r="B70" s="9"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
-      <c r="I70" s="14" t="str">
+      <c r="A70" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="9">
+        <v>500</v>
+      </c>
+      <c r="C70" s="9">
+        <v>120</v>
+      </c>
+      <c r="D70" s="9">
+        <v>400</v>
+      </c>
+      <c r="E70" s="9">
+        <v>300</v>
+      </c>
+      <c r="F70" s="9">
+        <v>0</v>
+      </c>
+      <c r="G70" s="9">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
+        <v>120</v>
+      </c>
+      <c r="I70" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J70" s="14" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J70" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K70" s="11"/>
-      <c r="L70" s="11"/>
-      <c r="M70" s="11"/>
-      <c r="N70" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="K70" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L70" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M70" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N70" s="12" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4C111E1-4C25-45F8-B604-CC042A95D521}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BA9C484-E404-468D-A8F5-B6B91206196F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4113,26 +4113,50 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="8"/>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="14" t="str">
+      <c r="A71" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="9">
+        <v>210</v>
+      </c>
+      <c r="C71" s="9">
+        <v>150</v>
+      </c>
+      <c r="D71" s="9">
+        <v>400</v>
+      </c>
+      <c r="E71" s="9">
+        <v>200</v>
+      </c>
+      <c r="F71" s="9">
+        <v>250</v>
+      </c>
+      <c r="G71" s="9">
+        <v>5</v>
+      </c>
+      <c r="H71" s="9">
+        <v>200</v>
+      </c>
+      <c r="I71" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J71" s="14" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J71" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="11"/>
-      <c r="L71" s="11"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="12"/>
+        <v>30</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L71" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N71" s="12" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BA9C484-E404-468D-A8F5-B6B91206196F}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DFD7CA2-A5A2-46B2-8CBE-D250C708E935}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -350,6 +350,9 @@
   </si>
   <si>
     <t xml:space="preserve">dussehra holiday </t>
+  </si>
+  <si>
+    <t>first time donated blood</t>
   </si>
 </sst>
 </file>
@@ -4159,48 +4162,96 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="8"/>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="14" t="str">
+      <c r="A72" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="9">
+        <v>300</v>
+      </c>
+      <c r="C72" s="9">
+        <v>140</v>
+      </c>
+      <c r="D72" s="9">
+        <v>350</v>
+      </c>
+      <c r="E72" s="9">
+        <v>200</v>
+      </c>
+      <c r="F72" s="9">
+        <v>200</v>
+      </c>
+      <c r="G72" s="9">
+        <v>4</v>
+      </c>
+      <c r="H72" s="9">
+        <v>200</v>
+      </c>
+      <c r="I72" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J72" s="14" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J72" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="11"/>
-      <c r="L72" s="11"/>
-      <c r="M72" s="11"/>
-      <c r="N72" s="12"/>
+        <v>50</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L72" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M72" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N72" s="12" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="8"/>
-      <c r="B73" s="9"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="14" t="str">
+      <c r="A73" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="9">
+        <v>360</v>
+      </c>
+      <c r="C73" s="9">
+        <v>140</v>
+      </c>
+      <c r="D73" s="9">
+        <v>300</v>
+      </c>
+      <c r="E73" s="9">
+        <v>250</v>
+      </c>
+      <c r="F73" s="9">
+        <v>350</v>
+      </c>
+      <c r="G73" s="9">
+        <v>7</v>
+      </c>
+      <c r="H73" s="9">
+        <v>40</v>
+      </c>
+      <c r="I73" s="14">
         <f t="shared" si="4"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J73" s="14" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J73" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="11"/>
-      <c r="L73" s="11"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="K73" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L73" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M73" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N73" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DFD7CA2-A5A2-46B2-8CBE-D250C708E935}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E99EB0E4-305D-4D51-8FB2-CF13F2248409}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4254,26 +4254,50 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="8"/>
-      <c r="B74" s="9"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="14" t="str">
+      <c r="A74" s="8">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="9">
+        <v>330</v>
+      </c>
+      <c r="C74" s="9">
+        <v>130</v>
+      </c>
+      <c r="D74" s="9">
+        <v>350</v>
+      </c>
+      <c r="E74" s="9">
+        <v>200</v>
+      </c>
+      <c r="F74" s="9">
+        <v>50</v>
+      </c>
+      <c r="G74" s="9">
+        <v>1</v>
+      </c>
+      <c r="H74" s="9">
+        <v>350</v>
+      </c>
+      <c r="I74" s="14">
         <f t="shared" ref="I74:I117" si="5">IF(SUM(B74:F74,H74)=0," ",SUM(B74:F74,H74))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J74" s="14" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J74" s="14">
         <f t="shared" ref="J74:J117" si="6">IF(I74=" ","",1440-I74)</f>
-        <v/>
-      </c>
-      <c r="K74" s="11"/>
-      <c r="L74" s="11"/>
-      <c r="M74" s="11"/>
-      <c r="N74" s="12"/>
+        <v>30</v>
+      </c>
+      <c r="K74" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L74" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N74" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E99EB0E4-305D-4D51-8FB2-CF13F2248409}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02901349-EBF1-4D52-84C2-678F75EC1721}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4300,26 +4300,50 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="8"/>
-      <c r="B75" s="9"/>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="14" t="str">
+      <c r="A75" s="8">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="9">
+        <v>600</v>
+      </c>
+      <c r="C75" s="9">
+        <v>140</v>
+      </c>
+      <c r="D75" s="9">
+        <v>400</v>
+      </c>
+      <c r="E75" s="9">
+        <v>150</v>
+      </c>
+      <c r="F75" s="9">
+        <v>0</v>
+      </c>
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
+        <v>150</v>
+      </c>
+      <c r="I75" s="14">
         <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J75" s="14" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J75" s="14">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K75" s="11"/>
-      <c r="L75" s="11"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="12"/>
+        <v>0</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N75" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02901349-EBF1-4D52-84C2-678F75EC1721}"/>
+  <xr:revisionPtr revIDLastSave="230" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8CEF8DF-8346-4081-AFEE-FD6EEDB70DD8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4346,26 +4346,50 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="8"/>
-      <c r="B76" s="9"/>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="14" t="str">
+      <c r="A76" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B76" s="9">
+        <v>400</v>
+      </c>
+      <c r="C76" s="9">
+        <v>130</v>
+      </c>
+      <c r="D76" s="9">
+        <v>400</v>
+      </c>
+      <c r="E76" s="9">
+        <v>200</v>
+      </c>
+      <c r="F76" s="9">
+        <v>0</v>
+      </c>
+      <c r="G76" s="9">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>300</v>
+      </c>
+      <c r="I76" s="14">
         <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J76" s="14" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J76" s="14">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K76" s="11"/>
-      <c r="L76" s="11"/>
-      <c r="M76" s="11"/>
-      <c r="N76" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K76" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L76" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M76" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N76" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="230" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8CEF8DF-8346-4081-AFEE-FD6EEDB70DD8}"/>
+  <xr:revisionPtr revIDLastSave="231" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10964060-5FA0-4E20-9038-6CB4294C7332}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,6 +353,9 @@
   </si>
   <si>
     <t>first time donated blood</t>
+  </si>
+  <si>
+    <t>exhausted day</t>
   </si>
 </sst>
 </file>
@@ -4392,26 +4395,50 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="8"/>
-      <c r="B77" s="9"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="14" t="str">
+      <c r="A77" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="9">
+        <v>500</v>
+      </c>
+      <c r="C77" s="9">
+        <v>150</v>
+      </c>
+      <c r="D77" s="9">
+        <v>200</v>
+      </c>
+      <c r="E77" s="9">
+        <v>200</v>
+      </c>
+      <c r="F77" s="9">
+        <v>150</v>
+      </c>
+      <c r="G77" s="9">
+        <v>3</v>
+      </c>
+      <c r="H77" s="9">
+        <v>200</v>
+      </c>
+      <c r="I77" s="14">
         <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J77" s="14" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J77" s="14">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K77" s="11"/>
-      <c r="L77" s="11"/>
-      <c r="M77" s="11"/>
-      <c r="N77" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="K77" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L77" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="M77" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N77" s="12" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10964060-5FA0-4E20-9038-6CB4294C7332}"/>
+  <xr:revisionPtr revIDLastSave="243" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21765E01-DDA7-42C4-9BAA-EDCB6654D3BC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4441,26 +4441,50 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="8"/>
-      <c r="B78" s="9"/>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="14" t="str">
+      <c r="A78" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="9">
+        <v>380</v>
+      </c>
+      <c r="C78" s="9">
+        <v>150</v>
+      </c>
+      <c r="D78" s="9">
+        <v>300</v>
+      </c>
+      <c r="E78" s="9">
+        <v>200</v>
+      </c>
+      <c r="F78" s="9">
+        <v>200</v>
+      </c>
+      <c r="G78" s="9">
+        <v>4</v>
+      </c>
+      <c r="H78" s="9">
+        <v>200</v>
+      </c>
+      <c r="I78" s="14">
         <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J78" s="14" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J78" s="14">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K78" s="11"/>
-      <c r="L78" s="11"/>
-      <c r="M78" s="11"/>
-      <c r="N78" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K78" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="L78" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M78" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="12" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="243" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21765E01-DDA7-42C4-9BAA-EDCB6654D3BC}"/>
+  <xr:revisionPtr revIDLastSave="244" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F382CFCA-73CD-4586-82D1-1F002C80261E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4483,7 +4483,7 @@
         <v>51</v>
       </c>
       <c r="N78" s="12" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\CAP776-Daily-Work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="13_ncr:1_{6751269C-88D7-464F-BCF9-4CDEC4DB43DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F382CFCA-73CD-4586-82D1-1F002C80261E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DBBECD-4ABC-4E08-92C6-E1AE80DA096A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4487,26 +4487,50 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="8"/>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="14" t="str">
+      <c r="A79" s="8">
+        <v>46324</v>
+      </c>
+      <c r="B79" s="9">
+        <v>300</v>
+      </c>
+      <c r="C79" s="9">
+        <v>150</v>
+      </c>
+      <c r="D79" s="9">
+        <v>300</v>
+      </c>
+      <c r="E79" s="9">
+        <v>200</v>
+      </c>
+      <c r="F79" s="9">
+        <v>250</v>
+      </c>
+      <c r="G79" s="9">
+        <v>5</v>
+      </c>
+      <c r="H79" s="9">
+        <v>200</v>
+      </c>
+      <c r="I79" s="14">
         <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J79" s="14" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J79" s="14">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K79" s="11"/>
-      <c r="L79" s="11"/>
-      <c r="M79" s="11"/>
-      <c r="N79" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="K79" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L79" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M79" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N79" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showObjects="none"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Documents\GitHub\CAP776-Daily-Work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21DBBECD-4ABC-4E08-92C6-E1AE80DA096A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{21DBBECD-4ABC-4E08-92C6-E1AE80DA096A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E78E798-BCF6-466F-BB00-5E420206BF9E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>exhausted day</t>
+  </si>
+  <si>
+    <t>networking CA</t>
   </si>
 </sst>
 </file>
@@ -4533,26 +4536,50 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="14" t="str">
+      <c r="A80" s="8">
+        <v>46325</v>
+      </c>
+      <c r="B80" s="9">
+        <v>300</v>
+      </c>
+      <c r="C80" s="9">
+        <v>180</v>
+      </c>
+      <c r="D80" s="9">
+        <v>200</v>
+      </c>
+      <c r="E80" s="9">
+        <v>250</v>
+      </c>
+      <c r="F80" s="9">
+        <v>300</v>
+      </c>
+      <c r="G80" s="9">
+        <v>6</v>
+      </c>
+      <c r="H80" s="9">
+        <v>200</v>
+      </c>
+      <c r="I80" s="14">
         <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J80" s="14" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J80" s="14">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K80" s="11"/>
-      <c r="L80" s="11"/>
-      <c r="M80" s="11"/>
-      <c r="N80" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L80" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M80" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N80" s="12" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="8"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/08f0634ad8470975/Documents/GitHub/CAP776-Daily-Work/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{21DBBECD-4ABC-4E08-92C6-E1AE80DA096A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E78E798-BCF6-466F-BB00-5E420206BF9E}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{21DBBECD-4ABC-4E08-92C6-E1AE80DA096A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F2D55B1-8DAD-4080-82FB-F0BC1E843281}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>networking CA</t>
+  </si>
+  <si>
+    <t>friend's birthday party</t>
   </si>
 </sst>
 </file>
@@ -4582,26 +4585,50 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="8"/>
-      <c r="B81" s="9"/>
-      <c r="C81" s="9"/>
-      <c r="D81" s="9"/>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="14" t="str">
+      <c r="A81" s="8">
+        <v>46326</v>
+      </c>
+      <c r="B81" s="9">
+        <v>540</v>
+      </c>
+      <c r="C81" s="9">
+        <v>140</v>
+      </c>
+      <c r="D81" s="9">
+        <v>200</v>
+      </c>
+      <c r="E81" s="9">
+        <v>200</v>
+      </c>
+      <c r="F81" s="9">
+        <v>150</v>
+      </c>
+      <c r="G81" s="9">
+        <v>3</v>
+      </c>
+      <c r="H81" s="9">
+        <v>200</v>
+      </c>
+      <c r="I81" s="14">
         <f t="shared" si="5"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="J81" s="14" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J81" s="14">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K81" s="11"/>
-      <c r="L81" s="11"/>
-      <c r="M81" s="11"/>
-      <c r="N81" s="12"/>
+        <v>10</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="L81" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M81" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N81" s="12" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="8"/>
